--- a/licitaciones_dashboard.xlsx
+++ b/licitaciones_dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,22 +491,202 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>PalabrasClave</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Categorias</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>CodigosCategoria</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CantidadReclamos</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>NombreUnidadCompra</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>DireccionUnidadCompra</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>RutOrganismo</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>NombreUsuarioResponsable</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>CargoUsuarioResponsable</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>DiasCierreLicitacion</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FechaVisitaTerreno</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>DireccionVisitaTerreno</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>FechaPublicacionRespuestas</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>FechaAperturaTecnica</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>FechaAperturaEconomica</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>FechaEntregaAntecedentes</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>FechaEstimadaAdjudicacion</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>FechaEstimadaFirma</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>ModalidadPago</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>TiempoDuracionContrato</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>UnidadTiempoDuracionContrato</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>TipoDuracionContrato</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>EsRenovable</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>PermiteSubcontratacion</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>ExtensionPlazoAutomatica</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>NombreResponsablePago</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>EmailResponsablePago</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>NombreResponsableContrato</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>EmailResponsableContrato</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>FonoResponsableContrato</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>CantidadItems</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>NombresItems</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>TipoActoAdjudicacion</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>NumeroActoAdjudicacion</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>FechaActoAdjudicacion</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>NumeroOferentes</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>UrlActaAdjudicacion</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>ProveedoresAdjudicados</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>MontoAdjudicadoTotal</t>
         </is>
       </c>
     </row>
@@ -569,57 +749,179 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>area verde</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>70111700</t>
         </is>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>542</v>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>PLAN DE MANTENCION AREA VERDE Y CANCHA DE FUTBOL DEL ESTADIO FEDERICO SCHWAGER</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>SECRETARIA COMUNAL DE PLANIFICACION</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>BANNEN 70, CORONEL</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>69.151.200-2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>KATHERINE ANDREA GATICA CATRIL</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>APOYO TECNICO LICITACIONES Y MERCADO PUBLICO</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>2026-07-09T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-07-13T15:00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2026-07-13T15:00:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2026-08-14T18:00:00</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Verónica Sáez Rebolledo</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Javier Valencia Labarca</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Servicios de cuidado de céspedes</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4160-8-LP26</t>
+          <t>5325-17-LE26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CONSTRUCCION AREA VERDE ALTONA HUALPÉN</t>
+          <t>CONSTRUCCION ÁREA VERDE POBLACIÓN ESTADIO COMUNA DE ZAPALLAR</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Revocada</t>
+          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HUALPEN</t>
+          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hualpén</t>
+          <t>Zapallar</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -630,62 +932,190 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-06-02T13:25:10.927</t>
+          <t>2026-05-26T09:31:05.817</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-07T14:00:00</t>
+          <t>2026-06-10T15:30:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-09-10T16:17:00</t>
+          <t>2026-07-13T17:15:45.457</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>area verde</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>72131700</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>274</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>La Municipalidad de Hualpén requiere efectuar llamado a Licitación Pública bajo la modalidad de Suma Alzada y en la forma exigida en las presentes y demás antecedentes que forman parte del presente llamado, con el fin de contratar los servicios de construcción para ejecutar la construcción de un área verde, donde se incorpora ruta accesible mediante pavimento continuo y homogéneo, instalación de escaños inclusivos, máquinas de ejercicio para adultos mayores, máquinas de ejercicios inclusivas y para todo público. Además, se considera instalación de juegos infantiles de resorte, juegos infantiles de resorte inclusivos, plantación de arbolado, plantas e iluminación.</t>
-        </is>
-      </c>
+      <c r="P3" t="n">
+        <v>155</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>La Ilustre Municipalidad de Zapallar, en adelante e indistintamente la “MUNICIPALIDAD” o el “MUNICIPIO”, llama a licitación pública para la ejecución del proyecto “Construcción Área Verde Población Estadio, Localidad de La Laguna, Comuna de Zapallar”, que considera la construcción de áreas verdes, paradero, iluminación ornamental, señaléticas viales, ruta accesible y conformación de aceras, del sector sur de la Población Estadio, la cual se regulará por las Bases Administrativas Generales sancionadas por Decreto Alcaldicio N°231/2026, de fecha 26 de enero de 2026, el cual aprueba las Bases Administrativas Generales</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Licitaciones</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Germán Riesco Nº399</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>69.050.400-6</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>EILEEN MAGDALENA FERNANDEZ PEREZ</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Administrativa Secpla</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-06-03T17:30:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-10T15:32:00</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-06-10T15:33:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2026-07-17T16:19:00</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Maria Ignacia Gamboa Guajardo</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Sebastian Olivares Olivares</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Construcción de obras civiles</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=7hEcNgLupbwXG6JIe2XScvdsIjdmzScPigEZZXjzpAs=</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>538598-32-LR26</t>
+          <t>2199-13-LP26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Serv. aseo HOSMET mant. jardínes y áreas verdes</t>
+          <t>SERVICIO DE ASEO INTEGRAL Y MTTO. ÁREAS VERDES</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Publicada</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FREI MONTALVA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -695,10 +1125,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Providencia</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>350000000</v>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -706,263 +1138,38 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-07-13T11:54:52.843</t>
+          <t>2026-06-23T15:54:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-08-12T15:30:00</t>
+          <t>2026-07-13T15:00:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-09T17:00:00</t>
+          <t>2026-08-13T15:00:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>76111500</t>
         </is>
       </c>
-      <c r="O4" t="n">
-        <v>56</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Servicio de aseo de las dependencias del Hospital Metropolitano, con servicio de mantención de jardines y áreas verdes por 36 meses.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4160-6-LE26</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MEJORAMIENTO AREA VERDE LAS GARZAS HUALPÉN</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Revocada</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MUNICIPALIDAD DE HUALPEN</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Biobío </t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hualpén</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-01T13:22:23.877</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2026-07-01T11:06:00</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-09-25T11:07:00</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>72131700</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>274</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>La Municipalidad de Hualpén requiere efectuar llamado a Licitación Pública bajo la modalidad de Suma Alzada y en la forma exigida en las presentes y demás antecedentes que forman parte del presente llamado, con el fin de contratar los servicios de terminación de una Área Verde, obras que consideran la instalación de un juego modular de escalar, un modular combinado de calistenia y toldo, y placa recordatoria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5325-17-LE26</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CONSTRUCCION ÁREA VERDE POBLACIÓN ESTADIO COMUNA DE ZAPALLAR</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Zapallar</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-05-26T09:31:05.817</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-06-10T15:30:00</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-07-13T17:15:45.457</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>72131700</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>155</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>La Ilustre Municipalidad de Zapallar, en adelante e indistintamente la “MUNICIPALIDAD” o el “MUNICIPIO”, llama a licitación pública para la ejecución del proyecto “Construcción Área Verde Población Estadio, Localidad de La Laguna, Comuna de Zapallar”, que considera la construcción de áreas verdes, paradero, iluminación ornamental, señaléticas viales, ruta accesible y conformación de aceras, del sector sur de la Población Estadio, la cual se regulará por las Bases Administrativas Generales sancionadas por Decreto Alcaldicio N°231/2026, de fecha 26 de enero de 2026, el cual aprueba las Bases Administrativas Generales</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2199-13-LP26</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SERVICIO DE ASEO INTEGRAL Y MTTO. ÁREAS VERDES</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FREI MONTALVA</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>350000000</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-06-23T15:54:00</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2026-07-13T15:00:00</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2026-08-13T15:00:00</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>76111500</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
+      <c r="P4" t="n">
         <v>41</v>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>El Instituto Nacional de Geriatría requiere contratar el servicio de
 aseo integral y mantención de áreas verdes necesarios para cumplir
@@ -973,42 +1180,749 @@
 diferentes áreas del Instituto Nacional de Geriatría.</t>
         </is>
       </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FRE</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Av. José Manuel Infante 370, Providencia</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>61.608.403-8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pedro Luis Materan Jaimes</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Adm. de Licitaciones y Contratos</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2026-07-03T18:30:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-13T15:01:00</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2026-07-13T15:01:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2026-08-13T15:00:00</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Juan Carlos Machuca</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Edmundo Leiva</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza de edificios</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4065-11-LE26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE ARBUSTOS Y PLANTAS MEJORAMIENTO ÁREAS VERDES Y BANDEJONES CENTRALES PUERTO INGENIERO IBÁÑEZ COMUNA DE RÍO IBÁÑEZ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Revocada</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>21584006</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-23T08:53:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-07-01T15:30:00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-07-10T17:30:00</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Artículos para plantas y animales / Productos de floricultura y silvicultura / Plantas con flor; Artículos para plantas y animales / Productos de floricultura y silvicultura / Plantas sin flor</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>10161600; 10161800</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ADQUISICIÓN DE ARBUSTOS Y PLANTAS, MEJORAMIENTO ÁREAS VERDES Y BANDEJONES CENTRALES PUERTO INGENIERO IBÁÑEZ, COMUNA DE RÍO IBÁÑEZ</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Dirección de Obras Municipales</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>69.253.100-0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>MARTIN TAIVOR DIAZ MUÑOZ</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>PROFESIONAL DIRECCIÓN DE OBRAS</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2026-06-26T16:30:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-01T15:35:00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2026-07-01T15:35:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2026-07-10T17:30:00</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Jorge Godoy Borquez</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>CRISTIAN SANTANA OJEDA</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Filodendros; Rosales</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>4160-6-LE26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO AREA VERDE LAS GARZAS HUALPÉN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Revocada</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE HUALPEN</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hualpén</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-01T13:22:23.877</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-07-01T11:06:00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:07:00</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>area verde</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>72131700</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>La Municipalidad de Hualpén requiere efectuar llamado a Licitación Pública bajo la modalidad de Suma Alzada y en la forma exigida en las presentes y demás antecedentes que forman parte del presente llamado, con el fin de contratar los servicios de terminación de una Área Verde, obras que consideran la instalación de un juego modular de escalar, un modular combinado de calistenia y toldo, y placa recordatoria.</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Secplan</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>PATRIA NUEVA 1035</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>69.264.400-k</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jorge Antonio Torres Roa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>PROFESIONAL SECPLAN</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2026-06-19T16:34:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-01T15:00:00</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>2026-07-01T15:00:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2026-09-25T11:07:00</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>RICARDO MUÑOZ BARRIGA</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>GASTON SANHUEZA MUÑOZ</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Construcción de obras civiles</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4160-8-LP26</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION AREA VERDE ALTONA HUALPÉN</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Revocada</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE HUALPEN</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hualpén</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-02T13:25:10.927</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-07-07T14:00:00</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-10T16:17:00</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>area verde</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>72131700</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>La Municipalidad de Hualpén requiere efectuar llamado a Licitación Pública bajo la modalidad de Suma Alzada y en la forma exigida en las presentes y demás antecedentes que forman parte del presente llamado, con el fin de contratar los servicios de construcción para ejecutar la construcción de un área verde, donde se incorpora ruta accesible mediante pavimento continuo y homogéneo, instalación de escaños inclusivos, máquinas de ejercicio para adultos mayores, máquinas de ejercicios inclusivas y para todo público. Además, se considera instalación de juegos infantiles de resorte, juegos infantiles de resorte inclusivos, plantación de arbolado, plantas e iluminación.</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Secplan</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>PATRIA NUEVA 1035</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>69.264.400-k</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jorge Antonio Torres Roa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>PROFESIONAL SECPLAN</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2026-06-26T16:52:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-07T14:45:00</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>2026-07-07T14:45:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2026-09-10T16:17:00</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>RICARDO MUÑOZ BARRIGA</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>GASTON SANHUEZA MUÑOZ</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Construcción de obras civiles</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4065-11-LE26</t>
+          <t>538598-32-LR26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARBUSTOS Y PLANTAS MEJORAMIENTO ÁREAS VERDES Y BANDEJONES CENTRALES PUERTO INGENIERO IBÁÑEZ COMUNA DE RÍO IBÁÑEZ</t>
+          <t>Serv. aseo HOSMET mant. jardínes y áreas verdes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Revocada</t>
+          <t>Publicada</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>21584006</v>
-      </c>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Providencia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -1016,47 +1930,169 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-06-23T08:53:00</t>
+          <t>2026-07-13T11:54:52.843</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-01T15:30:00</t>
+          <t>2026-08-12T15:30:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-07-10T17:30:00</t>
+          <t>2026-09-09T17:00:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Artículos para plantas y animales / Productos de floricultura y silvicultura / Plantas con flor; Artículos para plantas y animales / Productos de floricultura y silvicultura / Plantas sin flor</t>
+          <t>jardin; jardines; areas verdes</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>10161600; 10161800</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>46</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>ADQUISICIÓN DE ARBUSTOS Y PLANTAS, MEJORAMIENTO ÁREAS VERDES Y BANDEJONES CENTRALES PUERTO INGENIERO IBÁÑEZ, COMUNA DE RÍO IBÁÑEZ</t>
-        </is>
-      </c>
+          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>76111500</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Servicio de aseo de las dependencias del Hospital Metropolitano, con servicio de mantención de jardines y áreas verdes por 36 meses.</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>ABASTECIMIENTO</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>Holanda 060 (entrega por Vitacura 117)</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>61.979.450-8</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>BENJAMIN FUENTES DIAZ</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>PROFESIONAL LICITACIONES</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:30:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-12T15:31:00</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2026-08-12T15:31:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2026-09-09T17:00:00</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Daniela Villalobos</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Nicole Cañete</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza de edificios</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1271359-55-LE26</t>
+          <t>2735-109-LR26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EQUIP. DEPORTIVO DIDÁCTICO FUNGIBLES JARDINERÍA</t>
+          <t>Mantención Áreas Verdes comuna de Lo Barnechea</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1066,12 +2102,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1081,122 +2117,49 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lampa</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>34300000</v>
-      </c>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>CLF</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-07-02T16:11:41.32</t>
+          <t>2026-06-09T17:45:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-14T15:00:00</t>
+          <t>2026-07-14T12:00:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-08-12T20:00:00</t>
+          <t>2026-08-31T23:59:00</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Alimentos, bebidas y tabaco / Frutas, verduras y frutos secos / Verduras; Artículos de fabricación y producción / Pinturas, diluyentes y accesorios para pintado / Pinturas; Artículos para estructuras, obras y construcciones / Materiales para terminaciones exteriores / Materiales para acabado; Equipamiento para laboratorios / Instrumentos de medida y experimentación / Suministros y equipos para tratamiento de enfermos; Equipamiento y suministros médicos / Equipamiento para instalaciones médicas / Sistemas de construcción de instalaciones médicas; Equipamiento y suministros médicos / Suministros para formación y estudios de medicina / Ayudas para la formación médica; Equipos, accesorios y suministros de oficina / Suministros de oficina / Suministros de escritorio; Equipos, suministros y accesorios deportivos y recreativos / Equipos para entrenamiento físico / Equipo de entrenamiento de pesas y resistencia; Equipos, suministros y accesorios deportivos y recreativos / Equipos y accesorios para camping y exterior / Muebles de camping; Herramientas y maquinaria en general / Herramientas manuales / Herramientas de jardinería; Instrumentos musicales, juegos, juguetes, artesanías y materiales educativos / Materiales, artículos y suministros didácticos profesionales y para el desarrollo personal / Materiales educativos sobre las relaciones de pareja y sexuales, embarazo precoz, maternidad y desarrollo del niño; Instrumentos musicales, juegos, juguetes, artesanías y materiales educativos / Materiales, artículos y suministros didácticos profesionales y para el desarrollo personal / Organismos vivos, especímenes conservados y materiales relacionados; Muebles y mobiliario / Muebles de alojamiento / Accesorios y muebles de bebé y niño; Muebles y mobiliario / Muebles de alojamiento / Muebles para el exterior; Productos de papel / Productos de papel / Papel de imprenta y escritura; Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>14111500; 27112000; 30151900; 31211500; 41116200; 42191600; 42301500; 43211500; 44121600; 49121600; 49201600; 50101500; 56101600; 56101800; 60103900; 60105900</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>20</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>La Corporación Municipal de Desarrollo Social de Lampa requiere la adquisición de equipos de ejercicio, modelos anatómicos maquetas y maniquíes, incluyendo lactancia, artículos de jardinería y otros artículos, destinados al equipamiento de CECOSF, para apoyar prestaciones de salud, actividades formativas y el mantenimiento de espacios comunitarios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2735-109-LR26</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Mantención Áreas Verdes comuna de Lo Barnechea</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Lo Barnechea</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CLF</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-09T17:45:00</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-07-14T12:00:00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2026-08-31T23:59:00</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
           <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>70111700</t>
         </is>
       </c>
-      <c r="O10" t="n">
+      <c r="P9" t="n">
         <v>338</v>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>De conformidad con lo dispuesto en la Ley Nº 18.695, Orgánica Constitucional de Municipalidades, y lo establecido en el Reglamento N°33 1 de 30 de octubre de 2025, que Aprueba el Reglamento de Organización Interna y Organigrama del municipio, resulta necesario la contratación del servicio de Mantención, Conservación y Reposición de Áreas Verdes Públicas de la comuna, ya sean plazas, parques, paseos, bandejones, jardines de inmuebles municipales u otros que formen parte de la administración municipal, para darle continuidad al servicio y poder contribuir a la mejor calidad de vida de sus habitantes.
 La mantención, conservación y reposición de las áreas verdes de la comuna, considera para ello al menos los siguientes aspectos:
@@ -1210,6 +2173,317 @@
 •	Apertura y cierre de las áreas verdes que cuenten con cierro exterior.</t>
         </is>
       </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Municipalidad de lo Barnechea - Adquisiciones - Consistorial</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>El Rodeo N° 12.777</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>69.255.200-8</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mauricio Salazar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-06-30T20:00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-14T12:01:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-07-14T12:01:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:59:00</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Carolina Villarroel Cuevas</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Carolina Villarroel Cuevas</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Servicios de sembradío o mantenimiento de jardines</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2723-48-LE26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Adq. Maquinaria y Accesorios Recup. Areas Verdes</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cerrada</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BUIN</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-24T16:32:41.61</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-07-14T10:45:00</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-10-14T18:00:00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Herramientas y maquinaria en general / Herramientas manuales / Herramientas de corte, estaje y punzones</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>27111500</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>704</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Consiste en adquirir maquinaria y accesorios para equipo del Programa Recuperación e Implementación de Paisajismo, Mobiliario y otros lugares de encuentro comunal 2026, unidad de áreas verdes. Dirección de Medio Ambiente, Aseo y Ornato, Comuna de Buin, destinada a la Unidad de Parque Automotriz de la Dirección de Medio Ambiente, Aseo y Ornato, con el propósito de apoyar y optimizar sus labores.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE BUIN_ SECPLA</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>CARLOS CONDELL  415</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>69.072.500-2</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>MACARENA ANDREA MOLINA COLIPI</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>FUNCIONARIA SECPLA</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-07-07T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-14T11:00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-07-14T11:00:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-10-14T18:00:00</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Jorge Diaz Caceres</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Claudio Ronda Plaza</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Sierras</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1272,32 +2546,180 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>jardin</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>76111500</t>
         </is>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>141</v>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Servicio de Aseo y Mantención de Jardín para la Dirección Regional de Turismo, Araucanía por 24 meses</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Direccion Regional de la Araucania</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Thiers N°631</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>60.704.000-1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mauricio Arturo Villalobos Lagos</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Encargado Administrativo</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2026-06-10T23:59:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:01:00</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:01:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2026-07-22T12:14:00</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2026-07-28T00:00:00</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Mauricio Villalobos Lagos</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>SANDRA MOREIRA GUZMÁN</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza de edificios</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>Resolucion</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>2026-07-14T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=ljunwP1AovdMS1NrmIRr3RBh4k0UvhrKPgNQXFyIYFw=</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ALEMSI SERVICIOS LIMITADA</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2723-48-LE26</t>
+          <t>1271359-55-LE26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Adq. Maquinaria y Accesorios Recup. Areas Verdes</t>
+          <t>EQUIP. DEPORTIVO DIDÁCTICO FUNGIBLES JARDINERÍA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1312,7 +2734,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE BUIN</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1322,10 +2744,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>34300000</v>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -1333,76 +2757,198 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-06-24T16:32:41.61</t>
+          <t>2026-07-02T16:11:41.32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-14T10:45:00</t>
+          <t>2026-07-14T15:00:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-10-14T18:00:00</t>
+          <t>2026-08-12T20:00:00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Herramientas y maquinaria en general / Herramientas manuales / Herramientas de corte, estaje y punzones</t>
+          <t>jardin</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>27111500</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>704</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Consiste en adquirir maquinaria y accesorios para equipo del Programa Recuperación e Implementación de Paisajismo, Mobiliario y otros lugares de encuentro comunal 2026, unidad de áreas verdes. Dirección de Medio Ambiente, Aseo y Ornato, Comuna de Buin, destinada a la Unidad de Parque Automotriz de la Dirección de Medio Ambiente, Aseo y Ornato, con el propósito de apoyar y optimizar sus labores.</t>
-        </is>
-      </c>
+          <t>Alimentos, bebidas y tabaco / Frutas, verduras y frutos secos / Verduras; Artículos de fabricación y producción / Pinturas, diluyentes y accesorios para pintado / Pinturas; Artículos para estructuras, obras y construcciones / Materiales para terminaciones exteriores / Materiales para acabado; Equipamiento para laboratorios / Instrumentos de medida y experimentación / Suministros y equipos para tratamiento de enfermos; Equipamiento y suministros médicos / Equipamiento para instalaciones médicas / Sistemas de construcción de instalaciones médicas; Equipamiento y suministros médicos / Suministros para formación y estudios de medicina / Ayudas para la formación médica; Equipos, accesorios y suministros de oficina / Suministros de oficina / Suministros de escritorio; Equipos, suministros y accesorios deportivos y recreativos / Equipos para entrenamiento físico / Equipo de entrenamiento de pesas y resistencia; Equipos, suministros y accesorios deportivos y recreativos / Equipos y accesorios para camping y exterior / Muebles de camping; Herramientas y maquinaria en general / Herramientas manuales / Herramientas de jardinería; Instrumentos musicales, juegos, juguetes, artesanías y materiales educativos / Materiales, artículos y suministros didácticos profesionales y para el desarrollo personal / Materiales educativos sobre las relaciones de pareja y sexuales, embarazo precoz, maternidad y desarrollo del niño; Instrumentos musicales, juegos, juguetes, artesanías y materiales educativos / Materiales, artículos y suministros didácticos profesionales y para el desarrollo personal / Organismos vivos, especímenes conservados y materiales relacionados; Muebles y mobiliario / Muebles de alojamiento / Accesorios y muebles de bebé y niño; Muebles y mobiliario / Muebles de alojamiento / Muebles para el exterior; Productos de papel / Productos de papel / Papel de imprenta y escritura; Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>14111500; 27112000; 30151900; 31211500; 41116200; 42191600; 42301500; 43211500; 44121600; 49121600; 49201600; 50101500; 56101600; 56101800; 60103900; 60105900</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>La Corporación Municipal de Desarrollo Social de Lampa requiere la adquisición de equipos de ejercicio, modelos anatómicos maquetas y maniquíes, incluyendo lactancia, artículos de jardinería y otros artículos, destinados al equipamiento de CECOSF, para apoyar prestaciones de salud, actividades formativas y el mantenimiento de espacios comunitarios.</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>LICITACIONES</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>Sargento aldea 898</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>70.954.200-1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>CRISTIAN MARCELO RIQUELME BECERRA</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Asistente administrativo</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2026-07-09T20:00:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-14T15:00:00</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-07-14T15:00:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2026-08-12T20:00:00</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>NICOLAS GUAJARDO</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Claudia Gonzáles</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Barras con pesas; Esqueleto, hueso o especímenes de concha; Estacionamientos para bicicletas; Hardware de vías carriles de cortina o biombos o cortinas de cubículo del paciente; Kit de grapadora; Mangas de herramientas; Maniquís humanos anatómicos para formación y estudios de medicina; Materiales educativos de formación sobre cuidado del bebé; Mesas de camping; Monitores o medidores de glucosa; Máquinas de ejercicios múltiples; Notebook, laptop o computador portátil excepto Tablet PC; Papel para impresora del ordenador; Pinturas al esmalte; Toldos; Verduras frescas; mudadores o accesorios</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>564953-38-CO26</t>
+          <t>852-26-LP26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE OBRAS CIVILES JARDIN G. BLANCHE</t>
+          <t>SERVICIO DE MANTENCIÓN DE ÁREAS VERDES MALLECO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
+          <t>Publicada</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>24000000</v>
+        <v>80000000</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1411,76 +2957,198 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-29T17:07:50.893</t>
+          <t>2026-07-14T18:07:12.863</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-05-14T17:59:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-14T15:55:32.273</t>
+          <t>2026-09-04T18:39:00</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>80111600</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>100</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Contratar los Servicios de obras para el mejoramiento de obras civiles en camino acceso de Jardín Infantil General Blanche.</t>
-        </is>
-      </c>
+          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>72102900</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>655</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>El objeto de la presente licitación es contratar el “SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES, PROVINCIA DE MALLECO, REGIÓN DE LA ARAUCANÍA AÑO 2026-2028”.</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Junji - IX Región</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICUÑA MACKENNA 914 </t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>KARIME HERRERA FIGUEROA</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>PROFESIONAL</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>2026-07-21T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:10:00</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>2026-08-03T16:10:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2026-09-04T18:39:00</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>TESORERÍA</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>JURÍDICO</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>Servicios de paisajismo, arquitectura paisajista</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>852-26-LP26</t>
+          <t>564953-38-CO26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE ÁREAS VERDES MALLECO</t>
+          <t>MEJORAMIENTO DE OBRAS CIVILES JARDIN G. BLANCHE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Publicada</t>
+          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Temuco</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>80000000</v>
+        <v>24000000</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1489,72 +3157,200 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-07-14T18:07:12.863</t>
+          <t>2026-04-29T17:07:50.893</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-03T16:00:00</t>
+          <t>2026-05-14T17:59:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-09-04T18:39:00</t>
+          <t>2026-07-14T15:55:32.273</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
+          <t>jardin</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>72102900</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>655</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>El objeto de la presente licitación es contratar el “SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES, PROVINCIA DE MALLECO, REGIÓN DE LA ARAUCANÍA AÑO 2026-2028”.</t>
-        </is>
-      </c>
+          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>80111600</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Contratar los Servicios de obras para el mejoramiento de obras civiles en camino acceso de Jardín Infantil General Blanche.</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Corporación de Educación y Salud de Las Condes</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>RIO LOA 8350 (360 RAM)</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>70.902.000-5</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paola Romero </t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Adquisiciones</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2026-05-12T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-15T09:00:00</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>2026-05-18T09:00:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:00:00</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Francisco Díaz</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Francisco Perez</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Servicios temporales de construcción</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=2GycfPKiV9b5GyZ0QeMzyfCaIb34YH7bccN+uHYh1lA=</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1469-97-L126</t>
+          <t>1164956-13-O126</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE ALIMENTOS PARA ANIMALES Y AVES DEL JARDÍN BOTÁNICO Y ARBORETUM, TAL2495, UNIVERSIDAD DE TALCA”</t>
+          <t xml:space="preserve">Mejoramiento Areas Verdes Plaza Merlot, Comuna de Buin </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Adjudicada</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>O1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1565,115 +3361,353 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>2026-06-17T15:16:00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-07-15T10:00:00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2027-07-15T23:59:00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Consultoria / Consultoria / Planificación y Factibilidad</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>104000000</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>El objeto de la contratación es la ejecución de obras cuya finalidad es la construcción de áreas verdes.</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Obra Publica</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Serrano #45</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>61.812.000-7</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Karin Kaempfe Vasquez</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2026-07-03T13:05:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-15T10:00:00</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>2026-07-15T10:00:00</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>2027-07-15T23:59:00</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Licitación Pública de Obra MINVU</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1469-97-L126</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>“ADQUISICIÓN DE ALIMENTOS PARA ANIMALES Y AVES DEL JARDÍN BOTÁNICO Y ARBORETUM, TAL2495, UNIVERSIDAD DE TALCA”</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Adjudicada</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>2026-06-19T09:25:00</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>2026-06-30T15:00:00</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>2026-07-15T12:12:47.727</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Artículos para plantas y animales / Alimento para animales / Alimento para aves de corral</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>10121600</t>
         </is>
       </c>
-      <c r="O15" t="n">
+      <c r="P16" t="n">
         <v>206</v>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>La Universidad de Talca requiere la provisión de alimentos para animales y aves
 (silvestres, exóticos y domésticos), aproximadamente 50 especies de la Unidad
 Jardín Botánico y Arboretum.</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>1164956-13-O126</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mejoramiento Areas Verdes Plaza Merlot, Comuna de Buin </t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-06-17T15:16:00</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:00:00</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>2027-07-15T23:59:00</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Consultoria / Consultoria / Planificación y Factibilidad</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>104000000</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>51</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>El objeto de la contratación es la ejecución de obras cuya finalidad es la construcción de áreas verdes.</t>
-        </is>
-      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Universidad de Talca</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Laboratorio Computacional, Facultad de Psicología, Universidad de Talca, Av. Lircay s/n</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Yoselin Patricia Pezoa Gonzalez</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ejecutiva de Compras</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2026-06-25T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-30T15:01:00</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>2026-06-30T15:01:00</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2026-07-14T18:00:00</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>Alimento para aves</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>Autorizacion</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>20-41780</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>2026-07-15T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=mA7sTlI+VVHWPPzHtujxMx36KoDy9SGTBeVJNGdc8NM=</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>PRISCILA DEL ROSARIO ALIAGA NÚÑEZ</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1734,22 +3768,166 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
           <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>70111700</t>
         </is>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>275</v>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Servicio de mantenimiento de jardines y espacios verdes</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Corp. Adm. del Poder Judicial -  Valparaiso</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Prat 779, piso 9</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>ALEJANDRO MUÑOZ</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Administrativo de Mantenimiento</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>2026-05-28T15:26:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:02:00</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:02:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>2026-07-30T10:02:00</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Victor Villaroel Corrales</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Victor Villarroel Corrales</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>Servicios de sembradío o mantenimiento de jardines</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>Resolucion</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>26azvalp N106</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>2026-07-14T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=jJu9LyXh6+9s8/BwQv1qmTJxxdIGC6F/G+TBu54mFxk=</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>VÍCTOR ANDRÉS VAI MIRI RAGI HAOA HAOA</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1810,37 +3988,181 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>Artículos de fabricación y producción / Cuerdas, cadenas, cables, alambres y correas / Cadenas; Combustibles, lubricantes y anticorrosivos / Lubricantes y anticorrosivos / Lubricantes; Herramientas y maquinaria en general / Herramientas manuales / Herramientas de desbaste y acabado; Resinas, cauchos, espumas y elastómeros / Caucho y elastómeros / Plásticos termoplásticos</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>13102000; 15121500; 27111900; 31151600</t>
         </is>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>2694</v>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>La Ilustre Municipalidad de Arica - en adelante "La Municipalidad" - convoca a la licitación denominada “ADQ. REPUESTOS MAQUINAS PODADORAS, ORD.  N°524/2026, AREAS VERDES, DIMAO, IMA, NNR1”, dado la necesidad de la municipalidad de contar con los materiales de construcción y herramientas para el correcto funcionamiento de la oficina de logística, conforme a las especificaciones administrativas, técnicas y económicas establecidas en las presentes bases administrativas y técnicas, anexos y/o formularios</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>FINANZAS IMA</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>AV. RENATO ROCCA 1585</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nelson Nuñez Retamal</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Administrativo</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>2026-06-10T17:30:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:02:00</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:02:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>2026-09-30T17:30:00</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>MAURICIO ALBANES GOMEZ</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>MAURICIO ALBANES GOMEZ</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Aceite de engranajes; Cadenas corrientes; Limas; Nylon - Poliamida (PA)</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>Decreto</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>2026-07-09T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=s7riJfp0D7wlQl+Chjc3TZzhkYAfvRPvhT/Li0w76+g=</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>FERRETERIA AGRICOLA AQUALINE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2859-31-LP26</t>
+          <t>852-15-LP26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SERVICIO DE ASEO JARDINERIA Y GASFITERÍA</t>
+          <t>SERVICIO DE MANTENCIÓN DE ÁREAS VERDES CAUTÍN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Publicada</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1850,22 +4172,20 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copiapó</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>300000000</v>
-      </c>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -1873,47 +4193,170 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-07-15T13:32:59.52</t>
+          <t>2026-06-25T12:26:44.457</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00:00</t>
+          <t>2026-07-15T16:00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-08-14T19:00:00</t>
+          <t>2026-07-31T18:00:00</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>76111500</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>373</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>SERVICIO DE ASEO, JARDINERIA Y GASFITERÍA PARA LA FACULTAD DE CIENCIAS DE LA SALUD CAMPUS CORDILLERA Y  CASA MALDINI” DE LA UNIVERSIDAD DE ATACAMA.</t>
-        </is>
-      </c>
+          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>72102900</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>655</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>El objeto de la presente licitación es contratar el “SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES CLÁSICOS, PROVINCIA DE CAUTÍN, REGIÓN DE LA ARAUCANÍA AÑOS 2026-2028”. 
+La contratación del SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES CLÁSICOS, PROVINCIA DE CAUTÍN, REGIÓN DE LA ARAUCANÍA AÑOS 2026-2028” es bajo el sistema de precios unitarios descrito en las bases técnicas de la presente licitación.</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Junji - IX Región</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VICUÑA MACKENNA 914 </t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>70.072.600-2</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>KARIME HERRERA FIGUEROA</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>PROFESIONAL</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>2026-07-02T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-15T16:01:00</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>2026-07-15T16:01:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>2026-07-31T18:00:00</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>TESORERÍA</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>JURÍDICO</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Servicios de paisajismo, arquitectura paisajista</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5300-51-LP26</t>
+          <t>4412-16-LP26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUCCION CANCHA DE PASTO SINTETICO Y AREA VERDE HUMBERTO MOATH </t>
+          <t>MEJORAMIENTO AREAS VERDES Y SENDA PEATONAL QUILPUÉ</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1928,7 +4371,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1938,7 +4381,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1949,33 +4392,661 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>2026-07-15T13:57:58.64</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-14T15:30:00</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:30:00</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>72131700</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>El objetivo es la ejecución de los siguientes proyectos:
+-Proyecto N°1, que contempla las obras de mejoramiento del área verde ubicada en Avenida Industrial con calle José Uribe, en el sector de Belloto Norte.
+-Proyecto N°2, que contempla las obras de mejoramiento del área verde ubicada en calle Cora Wargny, en el sector de El Sol.
+-Proyecto N°3, que contempla las obras de mejoramiento de una senda peatonal en sector La Paloma, entre las calles Recoleta y La Paloma.</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Secretaria Comunal de Planificación</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>General Velasquez 560</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>69.061.300-K</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SERGIO FRANCISCO ARTEAGA LAZCANO</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>PROFESIONAL</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:30:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-21T15:31:00</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>2026-08-21T15:31:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:30:00</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>ARACELLI ALVAREZ VERGARA</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>XIMENA OLIVARES CERPA</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Construcción de obras civiles</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3253-47-LR26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SERVICIO DE MANTENCION AREAS VERDES COMUNA PELLUHUE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Adjudicada</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>2135000000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-04-30T15:52:56.8</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:00:00</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-07-15T10:53:57.703</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza industrial / Eliminación y tratamiento de desechos / Recolección y eliminación de desechos</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>76121500</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>98</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>SE REQUIERE LA CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES, SERVICIO DE RECOLECCION DE RESIDUOS SOLIDOS DOMICILIARIOS, Y SERVICIOS DE ASEO, COMUNA DE PELLUHUE 2026, 2027 Y2028, SEGUN BASES TECNICAS Y ADMINISTRATIVAS</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Secretaría de  Planificación</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Avenida Padre Samuel Jofré 415 Curanipe</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>69.252.700-3</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>JOHANNA ESTUARDO YAÑEZ</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EJECUTIVA DE COMPRAS</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>2026-05-18T17:00:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-01T17:01:00</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>2026-06-01T17:01:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>2026-06-29T17:36:00</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>MARGARITA VILLASEÑOR JARA</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>MARIA LUZ REYES ORELLANA</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza de calles</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>Decreto</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>4960</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>2026-06-17T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=RDr61j8tTf7ceNubu4WgOOc7QobLxxoP/O3g6H8rhMM=</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>INDUSTRIAL SERVICES SPA</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2859-31-LP26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ASEO JARDINERIA Y GASFITERÍA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ATACAMA</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-15T13:32:59.52</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:00:00</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-08-14T19:00:00</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>76111500</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>373</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>SERVICIO DE ASEO, JARDINERIA Y GASFITERÍA PARA LA FACULTAD DE CIENCIAS DE LA SALUD CAMPUS CORDILLERA Y  CASA MALDINI” DE LA UNIVERSIDAD DE ATACAMA.</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>SECCIÓN ABASTECIMIENTO</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>COPAYAPU Nº 485 COPIAPÓ</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>71.236.700-8</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Natalia Acuña Delgado</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Asistente Administrativa</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>2026-07-24T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:01:00</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:01:00</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>2026-08-14T19:00:00</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>DANIEL HERNANDEZ MANCILLA</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>WILSON JOPIA CARMONA</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza de edificios</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>5300-51-LP26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CONSTRUCCION CANCHA DE PASTO SINTETICO Y AREA VERDE HUMBERTO MOATH </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Casablanca</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>2026-07-15T15:42:48.71</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>2026-08-10T15:00:00</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>2026-08-24T18:00:00</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>area verde</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>72131700</t>
         </is>
       </c>
-      <c r="O20" t="n">
+      <c r="P23" t="n">
         <v>222</v>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>La necesidad de intervenir y consolidar un espacio recreativo integral en la
 Villa Humberto Moath, mediante la transformación de la actual cancha de
@@ -1987,251 +5058,133 @@
 habitantes.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>4412-16-LP26</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>MEJORAMIENTO AREAS VERDES Y SENDA PEATONAL QUILPUÉ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Publicada</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-07-15T13:57:58.64</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>2026-08-14T15:30:00</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>2026-09-28T15:30:00</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>72131700</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>59</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>El objetivo es la ejecución de los siguientes proyectos:
--Proyecto N°1, que contempla las obras de mejoramiento del área verde ubicada en Avenida Industrial con calle José Uribe, en el sector de Belloto Norte.
--Proyecto N°2, que contempla las obras de mejoramiento del área verde ubicada en calle Cora Wargny, en el sector de El Sol.
--Proyecto N°3, que contempla las obras de mejoramiento de una senda peatonal en sector La Paloma, entre las calles Recoleta y La Paloma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>3880-46-LP26</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CONSTRUCCIÓN ÁREA VERDE EL MIRADOR III COMUNA DE</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>193990000</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-06-25T10:43:34.68</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>2026-07-15T15:00:00</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>2026-08-17T10:05:00</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>80111600</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>357</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>CONSTRUCCIÓN ÁREA VERDE EL MIRADOR III, COMUNA DE MAULE, SECPLAN SEGUN BASES Y ARCHIVOS ADJUNTOS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>3253-47-LR26</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>SERVICIO DE MANTENCION AREAS VERDES COMUNA PELLUHUE</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Adjudicada</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Pelluhue</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>2135000000</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-04-30T15:52:56.8</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2026-06-01T15:00:00</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:53:57.703</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Servicios de limpieza industrial / Eliminación y tratamiento de desechos / Recolección y eliminación de desechos</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>76121500</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>98</v>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>SE REQUIERE LA CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES, SERVICIO DE RECOLECCION DE RESIDUOS SOLIDOS DOMICILIARIOS, Y SERVICIOS DE ASEO, COMUNA DE PELLUHUE 2026, 2027 Y2028, SEGUN BASES TECNICAS Y ADMINISTRATIVAS</t>
-        </is>
-      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>DIPLAD</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>CONSTITUCION 111</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>69.061.400-6</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>FELIPE EDUARDO NUÑEZ CHEUQUE</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>ARQUITECTO</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>2026-07-29T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-10T15:05:00</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>2026-08-10T15:05:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>2026-08-24T18:00:00</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>VICTOR QUINTEROS</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>YURI RODRIGUEZ REYES</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Construcción de obras civiles</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>852-15-LP26</t>
+          <t>3880-46-LP26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE ÁREAS VERDES CAUTÍN</t>
+          <t>CONSTRUCCIÓN ÁREA VERDE EL MIRADOR III COMUNA DE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2246,20 +5199,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Temuco</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>193990000</v>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -2267,38 +5222,157 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-06-25T12:26:44.457</t>
+          <t>2026-06-25T10:43:34.68</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-15T16:00:00</t>
+          <t>2026-07-15T15:00:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-31T18:00:00</t>
+          <t>2026-08-17T10:05:00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
+          <t>area verde</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>72102900</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>655</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>El objeto de la presente licitación es contratar el “SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES CLÁSICOS, PROVINCIA DE CAUTÍN, REGIÓN DE LA ARAUCANÍA AÑOS 2026-2028”. 
-La contratación del SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES CLÁSICOS, PROVINCIA DE CAUTÍN, REGIÓN DE LA ARAUCANÍA AÑOS 2026-2028” es bajo el sistema de precios unitarios descrito en las bases técnicas de la presente licitación.</t>
-        </is>
-      </c>
+          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>80111600</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>357</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CONSTRUCCIÓN ÁREA VERDE EL MIRADOR III, COMUNA DE MAULE, SECPLAN SEGUN BASES Y ARCHIVOS ADJUNTOS.</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Municipalidad de Maule</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Balmaceda 350</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>69.110.900-3</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jaime Meza Valenzuela</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>ASISTENTE COORDINACION COMPRAS MUNICIPAL</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>2026-07-09T16:00:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-15T15:00:00</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>2026-07-15T15:00:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>2026-08-17T10:05:00</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Departamento de Finanzas</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Secretario Comunal de Planificación</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Servicios temporales de construcción</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AU24" t="inlineStr"/>
+      <c r="AV24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr"/>
+      <c r="AX24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2361,33 +5435,159 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>jardin; jardines; areas verdes</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>70111700</t>
         </is>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>386</v>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t xml:space="preserve">SE REQUIERE LA CONTRATACIÓN DEL SERVICIO DE MANTENIMIENTO DE JARDÍNES Y ÁREAS VERDES PARA DEPENDENCIAS DE LA DIRECCIÓN DEL SERVICIO DE SALUD METROPOLITANO SUR ORIENTE, SEGÚN BASES APROBADAS POR RES. EXENTA N°1707/2026. 
 </t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Bienes y Servicios</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Av. Concha y Toro Nº 3459</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>61.608.500-K</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mauricio Claudio Muñoz Garcia</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Profesional Compras</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>2026-07-30T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-10T15:02:00</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>2026-08-10T15:02:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>2026-09-28T19:00:00</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:00:00</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Jonathan Levican Reyes</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Víctor Araya Retamal</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Servicios de sembradío o mantenimiento de jardines</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>584264-33-LR26</t>
+          <t>1219241-5-LE26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MANT. AREAS VERDES COMUNA INDEPENDENCIA</t>
+          <t>Adquisición de 2 Chipeadoras para áreas verdes.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2397,12 +5597,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>CORPORACIÓN MUNICIPAL PUEBLITO DE LAS VIZCACHAS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2412,7 +5612,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Independencia</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -2423,37 +5623,2192 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>2026-07-17T18:07:50.497</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-07-23T16:20:00</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-07-25T17:00:00</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Servicios de producción y fabricación industrial / Fabricación de maquinarias y equipos de transporte / Fabricación de maquinarias</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>73161500</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Adquisición de dos 2 chipeadoras nuevas para la ejecución de labores de manejo y reducción de residuos vegetales provenientes de trabajos de poda, mantención de áreas verdes y manejo forestal. Los oferentes deberán presentar una cotización detallada, conforme a las especificaciones técnicas adjuntas, indicando como mínimo la marca, modelo, características técnicas del equipo ofertado, plazo de entrega, garantía y cualquier otro antecedente que permita verificar el cumplimiento íntegro de los requerimientos establecidos. Solo se evaluarán las ofertas que cumplan con las especificaciones técnicas solicitadas.</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE ADQUISICIONES</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>Camino San José de Maipo 05109</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>65.108.319-2</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>LARISA LEGUIZAMON</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>COORDINADORA</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>2026-07-20T09:00:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:00:00</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>2026-07-23T21:00:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>2026-07-25T17:00:00</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>2026-07-27T00:00:00</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Larissa Leguizamon</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Claudio Aranguiz</t>
+        </is>
+      </c>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>Servicios de fabricación de maquinaria o equipos agrícolas</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="inlineStr"/>
+      <c r="AV26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr"/>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2289-33-LP26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CONSTRUCCION MULTICANCHA Y MEJORAMIENTO AREA VERDE VILLAS UNIDAS FRUTILLAR</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cerrada</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Frutillar</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>164509829</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-06-17T08:34:52</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:05:00</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:00:00</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>area verde</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>72131700</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>324</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>La presente licitación tiene por objeto la contratación de la ejecución de la obra "CONSTRUCCION MULTICANCHA RECREATIVA Y MEJORAMIENTO AREA VERDE, VILLAS UNIDAS, COMUNA DE FRUTILLAR"</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE FRUTILLAR</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>AVDA. ALESSANDRI S/N FRENTE A PLAZA FRUTILLAR ALTO</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>69.220.700-9</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Victor Hugo Mayorga Alvarado  </t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Adm. secplac</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>2026-07-07T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-20T09:00:00</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>2026-07-20T09:00:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:00:00</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>GILDA ALVARADO</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>CRISTABEL GALLEGOS</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>Construcción de obras civiles</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>584264-33-LR26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MANT. AREAS VERDES COMUNA INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Publicada</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Independencia</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>2026-07-17T11:09:49.967</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>2026-08-17T15:05:00</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>2026-10-06T17:30:00</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>70111700</t>
         </is>
       </c>
-      <c r="O26" t="n">
+      <c r="P28" t="n">
         <v>1291</v>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Asegurar la mantención, mejoramiento, reparación, construcción y desarrollo integral de las áreas verdes de la comuna de Independencia, garantizando la limpieza constante y completa de todos los espacios de plaza dura, caminerías, mobiliario urbano y zonas vegetales. Lo anterior se señala como referencia, el oferente deberá regirse por lo señalado en las Bases Técnicas y anexos.</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>DIRECCION DE SECPLA</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>AVDA. INDEPENDENCIA N° 753, INDEPENDENCIA</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>69.255.500-7</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Katherine Ruiz</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Profesional Licitaciones</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>2026-08-06T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-17T15:10:00</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>2026-08-17T15:10:00</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>2026-10-06T17:30:00</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>LUIS MEDEL FLORES</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>MARTA OLGUIN COUSIÑO</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>Servicios de sembradío o mantenimiento de parques</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr"/>
+      <c r="AX28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3656-139-L126</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES Y RIEGO DE BIENES NACIONALES DE USO PUBLICO PARA LA MUNICIPALIDAD DE REQUÍNOA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cerrada</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Requinoa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-07-10T13:29:39.443</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:01:00</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-07-29T18:09:00</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>80111600</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>171</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES Y RIEGO DE BIENES NACIONALES DE USO PUBLICO PARA LA MUNICIPALIDAD DE REQUÍNOA</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Requínoa</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Comercio 121 Municipalidad de Requínoa</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>69.081.300-9</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>MARIANELA ROJAS</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>MERCADO PUBLICO</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>2026-07-15T10:00:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:02:00</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:02:00</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>2026-07-29T18:09:00</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIEGO MORALES </t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DIEGO MORALES </t>
+        </is>
+      </c>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>Mano de obra temporal</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4168-68-LE26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CONCESIÓN MANTENCIÓN ÁREAS VERDES VILLA NUEVA PANIMÁVIDA Y RARIMÁVIDA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Adjudicada</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Maule </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-06-15T17:41:09.183</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-06-25T11:00:00</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:03:47.713</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>72102900</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>485</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>La Ilustre Municipalidad de Colbún, en adelante la “Municipalidad”, como Mandante y Unidad Técnica, llama a propuesta pública para contratar la concesión para mantención de las áreas verdes de las Villas Nueva Panimávida y Rarimávida de acuerdo a las Bases Administrativas y otros antecedentes de licitación.</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Municipalidad</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>Adolfo Novoa 419</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>69.130.500-7</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Camilo Ignacio Sepulveda Tobar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>ASISTENTE DE SEPCLA</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>2026-06-22T21:24:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-25T13:00:00</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>2026-06-25T13:00:00</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>2026-07-30T16:36:00</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Luis Muñoz Torres</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Yesica Gonzáles Parra</t>
+        </is>
+      </c>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Servicios de barrido de carreteras o aparcamientos (estacionamientos)</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr">
+        <is>
+          <t>Decreto</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="AV30" t="inlineStr">
+        <is>
+          <t>2026-07-13T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=6Jmg7by7tUE+1k0PNqjfP1V4ZIDzKLz1x2dYp6b9PJs=</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>DOMINGO ANTONIO ALFARO VASQUEZ</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4412-13-LP26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTOS PLAZOLETAS Y ÁREA VERDE QUILPUÉ 1.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cerrada</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Quilpué</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-06-16T16:43:35.693</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:30:00</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-08-31T15:30:00</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>area verde</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>72131700</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>-Proyecto N°1, que contempla las obras de mejoramiento de la plazoleta ubicada en la esquina de calles Buzo Sobenes con Almirante Gerken, en población Teniente Serrano.
+-Proyecto N°2, que contempla las obras de mejoramiento de la plazoleta ubicada en la esquina de calles Lago Lanalhue con Marga Marga, en población Porvenir.
+-Proyecto N°3, que contempla las obras de mejoramiento del área verde ubicado en la esquina de calles Ramón Ángel Jara con Marga Marga, en población Ingeniero Hyatt.</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Secretaria Comunal de Planificación</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>General Velasquez 560</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>69.061.300-K</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SERGIO FRANCISCO ARTEAGA LAZCANO</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>PROFESIONAL</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>2026-07-03T18:30:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:31:00</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:31:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>2026-08-31T15:30:00</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>ARACELLI ALVAREZ VERGARA</t>
+        </is>
+      </c>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>XIMENA OLIVARES CERPA</t>
+        </is>
+      </c>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>Construcción de obras civiles</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>5482-75-LE26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Implementación de áreas verdes</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-08T08:50:48.033</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:01:00</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>2026-08-31T17:45:00</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Producción, administración y protección de cultivos / Sembradío de plantaciones y cultivos</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>70141800</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>277</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Implementación de una nueva área verde con diversidad de especies nativas, consolidando un Bosque de Bolsillo, en el Parque
+Botánico de la comuna, las cuales tienen como objetivo regenerar suelos degradados de manera rápida y eficiente teniendo una alta
+efectividad a corto plazo, considerando un año desde la plantación oficial.
+El plazo para la ejecución del programano podrá ser superior a 4 meses, contados desde el día siguiente a la suscripción delActa
+de Inicio.
+</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>SECPLANUNOA</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>AV. IRARRAZAVAL 3550 - PISO 3º. SECPLA</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>69.070.500-1</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>JUAN PABLO JIMENEZ TORRES</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>PROFESIONAL SECPLA</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>2026-07-14T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:02:00</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:02:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>2026-08-31T17:45:00</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>alejandra naranjo</t>
+        </is>
+      </c>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>nicolas preus</t>
+        </is>
+      </c>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="inlineStr">
+        <is>
+          <t>Servicios de sembradío de cultivos</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=1efMHKv/qfhpYYOSbY/IMxp4XHEr9tdfzFxW4Zetmf0=</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2673-45-LE26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ADQUISICION INSUMOS Y ACCESORIOS AREAS VERDES</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Melipilla</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-05-29T15:54:52.15</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:00:00</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>2026-07-17T12:18:44.82</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Equipamiento para el acondicionamiento, distribución y filtrado de fluidos / Bombas y compresores industriales / Bombas</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>40151500</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>392</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>“ADQUISICIÓN INSUMOS Y ACCESORIOS PARA DEPARTAMENTO DE AREAS VERDES DGA”</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>SECRETARIA PLANIFICACION</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>SILVA CHAVEZ   480</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>69.072.900-8</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Francisco José Sandoval Domínguez</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>SUPERVISOR</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>2026-06-11T16:00:00</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:15:00</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>2026-06-19T10:15:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>2026-08-19T19:56:00</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>MARCIA WERCHEZ SANTIBAÑEZ</t>
+        </is>
+      </c>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>FLORENCIO VALDOVINOS REYES</t>
+        </is>
+      </c>
+      <c r="AP33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr"/>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="inlineStr">
+        <is>
+          <t>Bombas de agua</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AU33" t="inlineStr"/>
+      <c r="AV33" t="inlineStr"/>
+      <c r="AW33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=1mm3A2VlyIWnVXkWujQQGu3PEXnbiLZd7m45lKm3Ns0=</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3775-22-LR26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Mantención Áreas Verdes y Emergencias en Hijuelas</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Cerrada</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hijuelas</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>480000000</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-06-16T17:05:23.057</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:01:00</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:00:00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza industrial / Eliminación y tratamiento de desechos / Recolección y eliminación de desechos</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>76121500</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>120</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>“SERVICIO DE MANTENCIÓN, MEJORAMIENTO DE ÁREAS VERDES Y SERVICIO DE EMERGENCIAS PARA LABORES PREVENTIVAS, OPERATIVAS Y DE OBRAS MENORES EN COMUNA DE HIJUELAS”</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Secretaria Comunal De Planificacion</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>MANUEL RODRIGUEZ #1665, HIJUELAS</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>69.060.500-7</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Cristian Briones Arraño</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Profesional Secplan</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>2026-06-26T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:02:00</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:02:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:00:00</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Claudio Jamet Amaro</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Felipe Durán Rojas</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr"/>
+      <c r="AQ34" t="inlineStr"/>
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza de calles</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AU34" t="inlineStr"/>
+      <c r="AV34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr"/>
+      <c r="AX34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3882-58-LE26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO BODEGA MUNICIPAL AREAS VERDES COMUNA DE LLAY LLAY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cerrada</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Llay-Llay</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-01T15:38:00</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:10:00</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-07-31T17:00:00</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>72131700</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Se requiere contratar empresa idonea para ejecutar las obras correspondientes a  el mejoramiento del comedor, cocina, baños, camarines, pavimento patio exterior, sistema alcantarillado y agua potable, de recinto municipal siguiendo como referencia las especificaciones tecnicas.</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Llay Llay</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Avda. Balmaceda 174</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>69.060.400-0</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Cesar Ignacio Lobos Espinoza</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Profesional SECPLAC</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>2026-07-10T13:00:00</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:10:00</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:30:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>2026-07-31T17:00:00</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Dias</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I Municipalidad de Llay Llay </t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I Municipalidad de Llay Llay </t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr"/>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>Construcción de obras civiles</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AU35" t="inlineStr"/>
+      <c r="AV35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr"/>
+      <c r="AX35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>707423-49-LE26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ROPA DE CAMA PARA JARDINES Y SALAS CUNA ARAUCANIA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cerrada</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>46300000</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-06-18T09:49:03.22</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:01:00</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-08-11T16:30:00</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>jardin; jardines</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Muebles, accesorios, electrodomésticos y productos electrónicos / Ropa de cama, mantelerías, paños de cocina y toallas / Ropa de cama</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>52121500</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Fundación Integra, requiere de la adquisición de textiles, ropa de cama para jardines infantiles, salas cuna y oficina regional de fundación integra, Araucanía de conformidad a lo señalado en las presentes Bases Administrativas Especiales, Bases Administrativas Generales, Bases Técnicas, y Anexos.</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Regional Araucania</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Claro Solar Nº 1148</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Paola Macarena San Martín</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Analista</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>2026-07-02T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:05:00</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>2026-07-17T15:05:00</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>2026-08-11T16:30:00</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>MARIELA GARRIDO</t>
+        </is>
+      </c>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Patricio Hernandez Rojas</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr"/>
+      <c r="AR36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>Almohadas; Cobertor acolchado o plumón; Mantas o frazadas; Sábanas</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AU36" t="inlineStr"/>
+      <c r="AV36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr"/>
+      <c r="AX36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/licitaciones_dashboard.xlsx
+++ b/licitaciones_dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:BI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,44 +689,91 @@
           <t>MontoAdjudicadoTotal</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>ScoreMonto</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>ScoreTipo</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>ScoreRegion</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>ScoreEnfoque</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>ScoreReclamos</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>ScorePlazo</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>ScoreSubcontratacion</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>Accionable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2760-93-LE26</t>
+          <t>1057500-57-LP26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PLAN DE MANTENCION AREA VERDE Y CANCHA DE FUTBOL DEL ESTADIO FEDERICO SCHWAGER</t>
+          <t>SERVICIOS MANTENCION JARDINES Y AREAS VERDES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cerrada</t>
+          <t>Publicada</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CORONEL</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coronel</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Puente Alto</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>270000000</v>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -734,22 +781,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-07-02T11:41:00</t>
+          <t>2026-07-17T11:14:49.44</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-13T15:00:00</t>
+          <t>2026-08-10T15:01:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-08-14T18:00:00</t>
+          <t>2026-09-28T19:00:00</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>area verde</t>
+          <t>jardin; jardines; areas verdes</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -763,67 +810,72 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>542</v>
+        <v>386</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>PLAN DE MANTENCION AREA VERDE Y CANCHA DE FUTBOL DEL ESTADIO FEDERICO SCHWAGER</t>
+          <t xml:space="preserve">SE REQUIERE LA CONTRATACIÓN DEL SERVICIO DE MANTENIMIENTO DE JARDÍNES Y ÁREAS VERDES PARA DEPENDENCIAS DE LA DIRECCIÓN DEL SERVICIO DE SALUD METROPOLITANO SUR ORIENTE, SEGÚN BASES APROBADAS POR RES. EXENTA N°1707/2026. 
+</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>SECRETARIA COMUNAL DE PLANIFICACION</t>
+          <t>Bienes y Servicios</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>BANNEN 70, CORONEL</t>
+          <t>Av. Concha y Toro Nº 3459</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>69.151.200-2</t>
+          <t>61.608.500-K</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>KATHERINE ANDREA GATICA CATRIL</t>
+          <t>Mauricio Claudio Muñoz Garcia</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>APOYO TECNICO LICITACIONES Y MERCADO PUBLICO</t>
+          <t>Profesional Compras</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>2026-07-09T18:00:00</t>
+          <t>2026-07-30T18:00:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-13T15:00:00</t>
+          <t>2026-08-10T15:02:00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-07-13T15:00:00</t>
+          <t>2026-08-10T15:02:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2026-08-14T18:00:00</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr"/>
+          <t>2026-09-28T19:00:00</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:00:00</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr">
         <is>
           <t>Pago a 30 dias</t>
@@ -831,7 +883,7 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
@@ -851,23 +903,23 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Verónica Sáez Rebolledo</t>
+          <t>Jonathan Levican Reyes</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Javier Valencia Labarca</t>
+          <t>Víctor Araya Retamal</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr"/>
@@ -877,7 +929,7 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Servicios de cuidado de céspedes</t>
+          <t>Servicios de sembradío o mantenimiento de jardines</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -887,44 +939,75 @@
       <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>90</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5325-17-LE26</t>
+          <t>2859-31-LP26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CONSTRUCCION ÁREA VERDE POBLACIÓN ESTADIO COMUNA DE ZAPALLAR</t>
+          <t>SERVICIO DE ASEO JARDINERIA Y GASFITERÍA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
+          <t>Publicada</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ZAPALLAR</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t xml:space="preserve">Región de Atacama </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zapallar</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>300000000</v>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -932,93 +1015,93 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-05-26T09:31:05.817</t>
+          <t>2026-07-15T13:32:59.52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-06-10T15:30:00</t>
+          <t>2026-08-04T18:00:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-07-13T17:15:45.457</t>
+          <t>2026-08-14T19:00:00</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>area verde</t>
+          <t>jardin</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>72131700</t>
+          <t>76111500</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>155</v>
+        <v>373</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>La Ilustre Municipalidad de Zapallar, en adelante e indistintamente la “MUNICIPALIDAD” o el “MUNICIPIO”, llama a licitación pública para la ejecución del proyecto “Construcción Área Verde Población Estadio, Localidad de La Laguna, Comuna de Zapallar”, que considera la construcción de áreas verdes, paradero, iluminación ornamental, señaléticas viales, ruta accesible y conformación de aceras, del sector sur de la Población Estadio, la cual se regulará por las Bases Administrativas Generales sancionadas por Decreto Alcaldicio N°231/2026, de fecha 26 de enero de 2026, el cual aprueba las Bases Administrativas Generales</t>
+          <t>SERVICIO DE ASEO, JARDINERIA Y GASFITERÍA PARA LA FACULTAD DE CIENCIAS DE LA SALUD CAMPUS CORDILLERA Y  CASA MALDINI” DE LA UNIVERSIDAD DE ATACAMA.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Licitaciones</t>
+          <t>SECCIÓN ABASTECIMIENTO</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Germán Riesco Nº399</t>
+          <t>COPAYAPU Nº 485 COPIAPÓ</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>69.050.400-6</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>EILEEN MAGDALENA FERNANDEZ PEREZ</t>
+          <t>Natalia Acuña Delgado</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Administrativa Secpla</t>
+          <t>Asistente Administrativa</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2026-06-03T17:30:00</t>
+          <t>2026-07-24T18:00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-06-10T15:32:00</t>
+          <t>2026-08-04T18:01:00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-06-10T15:33:00</t>
+          <t>2026-08-04T18:01:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2026-07-17T16:19:00</t>
+          <t>2026-08-14T19:00:00</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr"/>
@@ -1029,12 +1112,12 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Dias</t>
+          <t>Meses</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1049,23 +1132,23 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Maria Ignacia Gamboa Guajardo</t>
+          <t>DANIEL HERNANDEZ MANCILLA</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Sebastian Olivares Olivares</t>
+          <t>WILSON JOPIA CARMONA</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr"/>
@@ -1075,37 +1158,60 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Construcción de obras civiles</t>
+          <t>Servicios de limpieza de edificios</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=7hEcNgLupbwXG6JIe2XScvdsIjdmzScPigEZZXjzpAs=</t>
-        </is>
-      </c>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2199-13-LP26</t>
+          <t>4412-16-LP26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SERVICIO DE ASEO INTEGRAL Y MTTO. ÁREAS VERDES</t>
+          <t>MEJORAMIENTO AREAS VERDES Y SENDA PEATONAL QUILPUÉ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cerrada</t>
+          <t>Publicada</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1115,22 +1221,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FREI MONTALVA</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>350000000</v>
-      </c>
+          <t>Quilpué</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -1138,17 +1242,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-06-23T15:54:00</t>
+          <t>2026-07-15T13:57:58.64</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-13T15:00:00</t>
+          <t>2026-08-14T15:30:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-09-28T15:30:00</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1158,79 +1262,76 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>76111500</t>
+          <t>72131700</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>El Instituto Nacional de Geriatría requiere contratar el servicio de
-aseo integral y mantención de áreas verdes necesarios para cumplir
-con los estándares de calidad, normativas, decretos ley y reglamentos
-IAAS que permitan a este recinto hospitalario cumplir con
-condiciones de bioseguridad para los pacientes y el personal en
-relación al manejo de desechos, control de suciedad visible en las
-diferentes áreas del Instituto Nacional de Geriatría.</t>
+          <t>El objetivo es la ejecución de los siguientes proyectos:
+-Proyecto N°1, que contempla las obras de mejoramiento del área verde ubicada en Avenida Industrial con calle José Uribe, en el sector de Belloto Norte.
+-Proyecto N°2, que contempla las obras de mejoramiento del área verde ubicada en calle Cora Wargny, en el sector de El Sol.
+-Proyecto N°3, que contempla las obras de mejoramiento de una senda peatonal en sector La Paloma, entre las calles Recoleta y La Paloma.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE GERIATRIA PRESIDENTE EDO FRE</t>
+          <t>Secretaria Comunal de Planificación</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Av. José Manuel Infante 370, Providencia</t>
+          <t>General Velasquez 560</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>61.608.403-8</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Pedro Luis Materan Jaimes</t>
+          <t>SERGIO FRANCISCO ARTEAGA LAZCANO</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Adm. de Licitaciones y Contratos</t>
+          <t>PROFESIONAL</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2026-07-03T18:30:00</t>
+          <t>2026-08-03T18:30:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-13T15:01:00</t>
+          <t>2026-08-21T15:31:00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-07-13T15:01:00</t>
+          <t>2026-08-21T15:31:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2026-08-13T15:00:00</t>
+          <t>2026-09-28T15:30:00</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr"/>
@@ -1241,12 +1342,12 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Meses</t>
+          <t>Horas</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1261,7 +1362,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1271,13 +1372,13 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Juan Carlos Machuca</t>
+          <t>ARACELLI ALVAREZ VERGARA</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Edmundo Leiva</t>
+          <t>XIMENA OLIVARES CERPA</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr"/>
@@ -1287,7 +1388,7 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Servicios de limpieza de edificios</t>
+          <t>Construcción de obras civiles</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1297,42 +1398,73 @@
       <c r="AX4" t="inlineStr"/>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4065-11-LE26</t>
+          <t>5300-51-LP26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARBUSTOS Y PLANTAS MEJORAMIENTO ÁREAS VERDES Y BANDEJONES CENTRALES PUERTO INGENIERO IBÁÑEZ COMUNA DE RÍO IBÁÑEZ</t>
+          <t xml:space="preserve">CONSTRUCCION CANCHA DE PASTO SINTETICO Y AREA VERDE HUMBERTO MOATH </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Revocada</t>
+          <t>Publicada</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>21584006</v>
-      </c>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Casablanca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -1340,89 +1472,100 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-06-23T08:53:00</t>
+          <t>2026-07-15T15:42:48.71</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-01T15:30:00</t>
+          <t>2026-08-10T15:00:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-07-10T17:30:00</t>
+          <t>2026-08-24T18:00:00</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>areas verdes</t>
+          <t>area verde</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Artículos para plantas y animales / Productos de floricultura y silvicultura / Plantas con flor; Artículos para plantas y animales / Productos de floricultura y silvicultura / Plantas sin flor</t>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>10161600; 10161800</t>
+          <t>72131700</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>46</v>
+        <v>222</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>ADQUISICIÓN DE ARBUSTOS Y PLANTAS, MEJORAMIENTO ÁREAS VERDES Y BANDEJONES CENTRALES PUERTO INGENIERO IBÁÑEZ, COMUNA DE RÍO IBÁÑEZ</t>
+          <t>La necesidad de intervenir y consolidar un espacio recreativo integral en la
+Villa Humberto Moath, mediante la transformación de la actual cancha de
+tierra en un complejo deportivo de pasto sintético dotado de sistemas de
+drenaje y canalización de aguas lluvias. Esta obra busca revertir el avanzado
+deterioro del sector y sus problemas de anegamiento invernal,
+promoviendo el desarrollo sustentable y la revitalización del entorno
+urbano de Casablanca para fortalecer el sentido de comunidad en sus
+habitantes.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Dirección de Obras Municipales</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
+          <t>DIPLAD</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>CONSTITUCION 111</t>
+        </is>
+      </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>MARTIN TAIVOR DIAZ MUÑOZ</t>
+          <t>FELIPE EDUARDO NUÑEZ CHEUQUE</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>PROFESIONAL DIRECCIÓN DE OBRAS</t>
+          <t>ARQUITECTO</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2026-06-26T16:30:00</t>
+          <t>2026-07-29T18:00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-07-01T15:35:00</t>
+          <t>2026-08-10T15:05:00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-07-01T15:35:00</t>
+          <t>2026-08-10T15:05:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2026-07-10T17:30:00</t>
+          <t>2026-08-24T18:00:00</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr"/>
@@ -1438,7 +1581,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Horas</t>
+          <t>Dias</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1453,7 +1596,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1463,23 +1606,23 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Jorge Godoy Borquez</t>
+          <t>VICTOR QUINTEROS</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>CRISTIAN SANTANA OJEDA</t>
+          <t>YURI RODRIGUEZ REYES</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Filodendros; Rosales</t>
+          <t>Construcción de obras civiles</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1489,41 +1632,70 @@
       <c r="AX5" t="inlineStr"/>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4160-6-LE26</t>
+          <t>584264-33-LR26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO AREA VERDE LAS GARZAS HUALPÉN</t>
+          <t>MANT. AREAS VERDES COMUNA INDEPENDENCIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Revocada</t>
+          <t>Publicada</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HUALPEN</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hualpén</t>
+          <t>Independencia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -1534,93 +1706,93 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-06-01T13:22:23.877</t>
+          <t>2026-07-17T11:09:49.967</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-01T11:06:00</t>
+          <t>2026-08-17T15:05:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-25T11:07:00</t>
+          <t>2026-10-06T17:30:00</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>area verde</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+          <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>72131700</t>
+          <t>70111700</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>274</v>
+        <v>1291</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>La Municipalidad de Hualpén requiere efectuar llamado a Licitación Pública bajo la modalidad de Suma Alzada y en la forma exigida en las presentes y demás antecedentes que forman parte del presente llamado, con el fin de contratar los servicios de terminación de una Área Verde, obras que consideran la instalación de un juego modular de escalar, un modular combinado de calistenia y toldo, y placa recordatoria.</t>
+          <t>Asegurar la mantención, mejoramiento, reparación, construcción y desarrollo integral de las áreas verdes de la comuna de Independencia, garantizando la limpieza constante y completa de todos los espacios de plaza dura, caminerías, mobiliario urbano y zonas vegetales. Lo anterior se señala como referencia, el oferente deberá regirse por lo señalado en las Bases Técnicas y anexos.</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Secplan</t>
+          <t>DIRECCION DE SECPLA</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>PATRIA NUEVA 1035</t>
+          <t>AVDA. INDEPENDENCIA N° 753, INDEPENDENCIA</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>69.264.400-k</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Jorge Antonio Torres Roa</t>
+          <t>Katherine Ruiz</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>PROFESIONAL SECPLAN</t>
+          <t>Profesional Licitaciones</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2026-06-19T16:34:00</t>
+          <t>2026-08-06T18:00:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-01T15:00:00</t>
+          <t>2026-08-17T15:10:00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-07-01T15:00:00</t>
+          <t>2026-08-17T15:10:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2026-09-25T11:07:00</t>
+          <t>2026-10-06T17:30:00</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr"/>
@@ -1631,12 +1803,12 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Dias</t>
+          <t>Meses</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1661,13 +1833,13 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>RICARDO MUÑOZ BARRIGA</t>
+          <t>LUIS MEDEL FLORES</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>GASTON SANHUEZA MUÑOZ</t>
+          <t>MARTA OLGUIN COUSIÑO</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr"/>
@@ -1677,7 +1849,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>Construcción de obras civiles</t>
+          <t>Servicios de sembradío o mantenimiento de parques</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1687,41 +1859,70 @@
       <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4160-8-LP26</t>
+          <t>1219241-5-LE26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CONSTRUCCION AREA VERDE ALTONA HUALPÉN</t>
+          <t>Adquisición de 2 Chipeadoras para áreas verdes.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Revocada</t>
+          <t>Publicada</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE HUALPEN</t>
+          <t>CORPORACIÓN MUNICIPAL PUEBLITO DE LAS VIZCACHAS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hualpén</t>
+          <t>Puente Alto</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -1732,96 +1933,100 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-06-02T13:25:10.927</t>
+          <t>2026-07-17T18:07:50.497</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-07T14:00:00</t>
+          <t>2026-07-23T16:20:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-09-10T16:17:00</t>
+          <t>2026-07-25T17:00:00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>area verde</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+          <t>Servicios de producción y fabricación industrial / Fabricación de maquinarias y equipos de transporte / Fabricación de maquinarias</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>72131700</t>
+          <t>73161500</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>La Municipalidad de Hualpén requiere efectuar llamado a Licitación Pública bajo la modalidad de Suma Alzada y en la forma exigida en las presentes y demás antecedentes que forman parte del presente llamado, con el fin de contratar los servicios de construcción para ejecutar la construcción de un área verde, donde se incorpora ruta accesible mediante pavimento continuo y homogéneo, instalación de escaños inclusivos, máquinas de ejercicio para adultos mayores, máquinas de ejercicios inclusivas y para todo público. Además, se considera instalación de juegos infantiles de resorte, juegos infantiles de resorte inclusivos, plantación de arbolado, plantas e iluminación.</t>
+          <t>Adquisición de dos 2 chipeadoras nuevas para la ejecución de labores de manejo y reducción de residuos vegetales provenientes de trabajos de poda, mantención de áreas verdes y manejo forestal. Los oferentes deberán presentar una cotización detallada, conforme a las especificaciones técnicas adjuntas, indicando como mínimo la marca, modelo, características técnicas del equipo ofertado, plazo de entrega, garantía y cualquier otro antecedente que permita verificar el cumplimiento íntegro de los requerimientos establecidos. Solo se evaluarán las ofertas que cumplan con las especificaciones técnicas solicitadas.</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Secplan</t>
+          <t>DEPARTAMENTO DE ADQUISICIONES</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>PATRIA NUEVA 1035</t>
+          <t>Camino San José de Maipo 05109</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>69.264.400-k</t>
+          <t>65.108.319-2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Jorge Antonio Torres Roa</t>
+          <t>LARISA LEGUIZAMON</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>PROFESIONAL SECPLAN</t>
+          <t>COORDINADORA</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2026-06-26T16:52:00</t>
+          <t>2026-07-20T09:00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-07-07T14:45:00</t>
+          <t>2026-07-23T21:00:00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-07-07T14:45:00</t>
+          <t>2026-07-23T21:00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2026-09-10T16:17:00</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr"/>
+          <t>2026-07-25T17:00:00</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2026-07-27T00:00:00</t>
+        </is>
+      </c>
       <c r="AF7" t="inlineStr">
         <is>
           <t>Pago a 30 dias</t>
@@ -1829,12 +2034,12 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Dias</t>
+          <t>Horas</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -1859,13 +2064,13 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>RICARDO MUÑOZ BARRIGA</t>
+          <t>Larissa Leguizamon</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>GASTON SANHUEZA MUÑOZ</t>
+          <t>Claudio Aranguiz</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr"/>
@@ -1875,7 +2080,7 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>Construcción de obras civiles</t>
+          <t>Servicios de fabricación de maquinaria o equipos agrícolas</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1885,16 +2090,45 @@
       <c r="AX7" t="inlineStr"/>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>60</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>538598-32-LR26</t>
+          <t>852-26-LP26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Serv. aseo HOSMET mant. jardínes y áreas verdes</t>
+          <t>SERVICIO DE MANTENCIÓN DE ÁREAS VERDES MALLECO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1904,25 +2138,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Providencia</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>80000000</v>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -1930,93 +2166,93 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-07-13T11:54:52.843</t>
+          <t>2026-07-14T18:07:12.863</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-08-12T15:30:00</t>
+          <t>2026-08-03T16:00:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-09-09T17:00:00</t>
+          <t>2026-09-04T18:39:00</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>jardin; jardines; areas verdes</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
+          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>76111500</t>
+          <t>72102900</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>56</v>
+        <v>655</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Servicio de aseo de las dependencias del Hospital Metropolitano, con servicio de mantención de jardines y áreas verdes por 36 meses.</t>
+          <t>El objeto de la presente licitación es contratar el “SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES, PROVINCIA DE MALLECO, REGIÓN DE LA ARAUCANÍA AÑO 2026-2028”.</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>ABASTECIMIENTO</t>
+          <t>Junji - IX Región</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Holanda 060 (entrega por Vitacura 117)</t>
+          <t xml:space="preserve">VICUÑA MACKENNA 914 </t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>61.979.450-8</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>BENJAMIN FUENTES DIAZ</t>
+          <t>KARIME HERRERA FIGUEROA</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>PROFESIONAL LICITACIONES</t>
+          <t>PROFESIONAL</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2026-08-02T15:30:00</t>
+          <t>2026-07-21T18:00:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-12T15:31:00</t>
+          <t>2026-08-03T16:10:00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-08-12T15:31:00</t>
+          <t>2026-08-03T16:10:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2026-09-09T17:00:00</t>
+          <t>2026-09-04T18:39:00</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr"/>
@@ -2027,7 +2263,7 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -2047,23 +2283,23 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Daniela Villalobos</t>
+          <t>TESORERÍA</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Nicole Cañete</t>
+          <t>JURÍDICO</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr"/>
@@ -2073,7 +2309,7 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>Servicios de limpieza de edificios</t>
+          <t>Servicios de paisajismo, arquitectura paisajista</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -2083,83 +2319,1042 @@
       <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>70</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>57</v>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>1271359-55-LE26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>EQUIP. DEPORTIVO DIDÁCTICO FUNGIBLES JARDINERÍA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Cerrada</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lampa</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>34300000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-02T16:11:41.32</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-07-14T15:00:00</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-08-12T20:00:00</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Alimentos, bebidas y tabaco / Frutas, verduras y frutos secos / Verduras; Artículos de fabricación y producción / Pinturas, diluyentes y accesorios para pintado / Pinturas; Artículos para estructuras, obras y construcciones / Materiales para terminaciones exteriores / Materiales para acabado; Equipamiento para laboratorios / Instrumentos de medida y experimentación / Suministros y equipos para tratamiento de enfermos; Equipamiento y suministros médicos / Equipamiento para instalaciones médicas / Sistemas de construcción de instalaciones médicas; Equipamiento y suministros médicos / Suministros para formación y estudios de medicina / Ayudas para la formación médica; Equipos, accesorios y suministros de oficina / Suministros de oficina / Suministros de escritorio; Equipos, suministros y accesorios deportivos y recreativos / Equipos para entrenamiento físico / Equipo de entrenamiento de pesas y resistencia; Equipos, suministros y accesorios deportivos y recreativos / Equipos y accesorios para camping y exterior / Muebles de camping; Herramientas y maquinaria en general / Herramientas manuales / Herramientas de jardinería; Instrumentos musicales, juegos, juguetes, artesanías y materiales educativos / Materiales, artículos y suministros didácticos profesionales y para el desarrollo personal / Materiales educativos sobre las relaciones de pareja y sexuales, embarazo precoz, maternidad y desarrollo del niño; Instrumentos musicales, juegos, juguetes, artesanías y materiales educativos / Materiales, artículos y suministros didácticos profesionales y para el desarrollo personal / Organismos vivos, especímenes conservados y materiales relacionados; Muebles y mobiliario / Muebles de alojamiento / Accesorios y muebles de bebé y niño; Muebles y mobiliario / Muebles de alojamiento / Muebles para el exterior; Productos de papel / Productos de papel / Papel de imprenta y escritura; Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>14111500; 27112000; 30151900; 31211500; 41116200; 42191600; 42301500; 43211500; 44121600; 49121600; 49201600; 50101500; 56101600; 56101800; 60103900; 60105900</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>La Corporación Municipal de Desarrollo Social de Lampa requiere la adquisición de equipos de ejercicio, modelos anatómicos maquetas y maniquíes, incluyendo lactancia, artículos de jardinería y otros artículos, destinados al equipamiento de CECOSF, para apoyar prestaciones de salud, actividades formativas y el mantenimiento de espacios comunitarios.</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>LICITACIONES</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Sargento aldea 898</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>70.954.200-1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>CRISTIAN MARCELO RIQUELME BECERRA</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Asistente administrativo</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-07-09T20:00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-14T15:00:00</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>2026-07-14T15:00:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2026-08-12T20:00:00</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>NICOLAS GUAJARDO</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Claudia Gonzáles</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Barras con pesas; Esqueleto, hueso o especímenes de concha; Estacionamientos para bicicletas; Hardware de vías carriles de cortina o biombos o cortinas de cubículo del paciente; Kit de grapadora; Mangas de herramientas; Maniquís humanos anatómicos para formación y estudios de medicina; Materiales educativos de formación sobre cuidado del bebé; Mesas de camping; Monitores o medidores de glucosa; Máquinas de ejercicios múltiples; Notebook, laptop o computador portátil excepto Tablet PC; Papel para impresora del ordenador; Pinturas al esmalte; Toldos; Verduras frescas; mudadores o accesorios</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="n">
+        <v>11.43333333333333</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>564953-38-CO26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MEJORAMIENTO DE OBRAS CIVILES JARDIN G. BLANCHE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Corporación de Educación y Salud de Las Condes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-04-29T17:07:50.893</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-05-14T17:59:00</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-07-14T15:55:32.273</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>80111600</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Contratar los Servicios de obras para el mejoramiento de obras civiles en camino acceso de Jardín Infantil General Blanche.</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Corporación de Educación y Salud de Las Condes</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>RIO LOA 8350 (360 RAM)</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>70.902.000-5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paola Romero </t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Adquisiciones</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-05-12T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-15T09:00:00</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2026-05-18T09:00:00</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:00:00</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Francisco Díaz</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Francisco Perez</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>Servicios temporales de construcción</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=2GycfPKiV9b5GyZ0QeMzyfCaIb34YH7bccN+uHYh1lA=</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1874-1-LE26</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Servicio Aseo y Mantención de Jardín</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Adjudicada</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE TURISMO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Temuco</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>19200000</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-06-03T08:42:00</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:00:00</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-07-14T18:01:58.787</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>76111500</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>141</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Servicio de Aseo y Mantención de Jardín para la Dirección Regional de Turismo, Araucanía por 24 meses</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Direccion Regional de la Araucania</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Thiers N°631</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>60.704.000-1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mauricio Arturo Villalobos Lagos</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Encargado Administrativo</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2026-06-10T23:59:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:01:00</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>2026-06-15T15:01:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2026-07-22T12:14:00</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2026-07-28T00:00:00</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Mauricio Villalobos Lagos</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>SANDRA MOREIRA GUZMÁN</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>Servicios de limpieza de edificios</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>Resolucion</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>2026-07-14T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=ljunwP1AovdMS1NrmIRr3RBh4k0UvhrKPgNQXFyIYFw=</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ALEMSI SERVICIOS LIMITADA</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2723-48-LE26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Adq. Maquinaria y Accesorios Recup. Areas Verdes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cerrada</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE BUIN</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Buin</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-06-24T16:32:41.61</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-07-14T10:45:00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-10-14T18:00:00</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>areas verdes</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Herramientas y maquinaria en general / Herramientas manuales / Herramientas de corte, estaje y punzones</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>27111500</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>704</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Consiste en adquirir maquinaria y accesorios para equipo del Programa Recuperación e Implementación de Paisajismo, Mobiliario y otros lugares de encuentro comunal 2026, unidad de áreas verdes. Dirección de Medio Ambiente, Aseo y Ornato, Comuna de Buin, destinada a la Unidad de Parque Automotriz de la Dirección de Medio Ambiente, Aseo y Ornato, con el propósito de apoyar y optimizar sus labores.</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE BUIN_ SECPLA</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>CARLOS CONDELL  415</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>69.072.500-2</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>MACARENA ANDREA MOLINA COLIPI</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FUNCIONARIA SECPLA</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2026-07-07T18:00:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-14T11:00:00</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>2026-07-14T11:00:00</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2026-10-14T18:00:00</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Horas</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Jorge Diaz Caceres</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Claudio Ronda Plaza</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>Sierras</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>2735-109-LR26</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Mantención Áreas Verdes comuna de Lo Barnechea</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Cerrada</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>LR</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Lo Barnechea</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>CLF</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>2026-06-09T17:45:00</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-07-14T12:00:00</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>2026-08-31T23:59:00</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>areas verdes</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>70111700</t>
         </is>
       </c>
-      <c r="P9" t="n">
+      <c r="P13" t="n">
         <v>338</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>De conformidad con lo dispuesto en la Ley Nº 18.695, Orgánica Constitucional de Municipalidades, y lo establecido en el Reglamento N°33 1 de 30 de octubre de 2025, que Aprueba el Reglamento de Organización Interna y Organigrama del municipio, resulta necesario la contratación del servicio de Mantención, Conservación y Reposición de Áreas Verdes Públicas de la comuna, ya sean plazas, parques, paseos, bandejones, jardines de inmuebles municipales u otros que formen parte de la administración municipal, para darle continuidad al servicio y poder contribuir a la mejor calidad de vida de sus habitantes.
 La mantención, conservación y reposición de las áreas verdes de la comuna, considera para ello al menos los siguientes aspectos:
@@ -2173,877 +3368,53 @@
 •	Apertura y cierre de las áreas verdes que cuenten con cierro exterior.</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>Municipalidad de lo Barnechea - Adquisiciones - Consistorial</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>El Rodeo N° 12.777</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>69.255.200-8</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Mauricio Salazar</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>2026-06-30T20:00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2026-07-14T12:01:00</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>2026-07-14T12:01:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2026-08-31T23:59:00</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Meses</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Carolina Villarroel Cuevas</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Carolina Villarroel Cuevas</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Servicios de sembradío o mantenimiento de jardines</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2723-48-LE26</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Adq. Maquinaria y Accesorios Recup. Areas Verdes</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE BUIN</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Buin</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-06-24T16:32:41.61</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2026-07-14T10:45:00</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2026-10-14T18:00:00</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>areas verdes</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Herramientas y maquinaria en general / Herramientas manuales / Herramientas de corte, estaje y punzones</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>27111500</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>704</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Consiste en adquirir maquinaria y accesorios para equipo del Programa Recuperación e Implementación de Paisajismo, Mobiliario y otros lugares de encuentro comunal 2026, unidad de áreas verdes. Dirección de Medio Ambiente, Aseo y Ornato, Comuna de Buin, destinada a la Unidad de Parque Automotriz de la Dirección de Medio Ambiente, Aseo y Ornato, con el propósito de apoyar y optimizar sus labores.</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>MUNICIPALIDAD DE BUIN_ SECPLA</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>CARLOS CONDELL  415</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>69.072.500-2</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>MACARENA ANDREA MOLINA COLIPI</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>FUNCIONARIA SECPLA</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>2026-07-07T18:00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2026-07-14T11:00:00</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>2026-07-14T11:00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>2026-10-14T18:00:00</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Horas</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Jorge Diaz Caceres</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Claudio Ronda Plaza</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>Sierras</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1874-1-LE26</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Servicio Aseo y Mantención de Jardín</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Adjudicada</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>SERVICIO NACIONAL DE TURISMO</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Temuco</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>19200000</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-06-03T08:42:00</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-06-15T15:00:00</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2026-07-14T18:01:58.787</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>jardin</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>76111500</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>141</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Servicio de Aseo y Mantención de Jardín para la Dirección Regional de Turismo, Araucanía por 24 meses</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Direccion Regional de la Araucania</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Thiers N°631</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>60.704.000-1</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Mauricio Arturo Villalobos Lagos</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Encargado Administrativo</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2026-06-10T23:59:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2026-06-15T15:01:00</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>2026-06-15T15:01:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>2026-07-22T12:14:00</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2026-07-28T00:00:00</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Meses</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Mauricio Villalobos Lagos</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>SANDRA MOREIRA GUZMÁN</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>Servicios de limpieza de edificios</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>Resolucion</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>2026-07-14T00:00:00</t>
-        </is>
-      </c>
-      <c r="AW11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=ljunwP1AovdMS1NrmIRr3RBh4k0UvhrKPgNQXFyIYFw=</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIAL ALEMSI SERVICIOS LIMITADA</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1271359-55-LE26</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>EQUIP. DEPORTIVO DIDÁCTICO FUNGIBLES JARDINERÍA</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lampa</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>34300000</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-07-02T16:11:41.32</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-07-14T15:00:00</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2026-08-12T20:00:00</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>jardin</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Alimentos, bebidas y tabaco / Frutas, verduras y frutos secos / Verduras; Artículos de fabricación y producción / Pinturas, diluyentes y accesorios para pintado / Pinturas; Artículos para estructuras, obras y construcciones / Materiales para terminaciones exteriores / Materiales para acabado; Equipamiento para laboratorios / Instrumentos de medida y experimentación / Suministros y equipos para tratamiento de enfermos; Equipamiento y suministros médicos / Equipamiento para instalaciones médicas / Sistemas de construcción de instalaciones médicas; Equipamiento y suministros médicos / Suministros para formación y estudios de medicina / Ayudas para la formación médica; Equipos, accesorios y suministros de oficina / Suministros de oficina / Suministros de escritorio; Equipos, suministros y accesorios deportivos y recreativos / Equipos para entrenamiento físico / Equipo de entrenamiento de pesas y resistencia; Equipos, suministros y accesorios deportivos y recreativos / Equipos y accesorios para camping y exterior / Muebles de camping; Herramientas y maquinaria en general / Herramientas manuales / Herramientas de jardinería; Instrumentos musicales, juegos, juguetes, artesanías y materiales educativos / Materiales, artículos y suministros didácticos profesionales y para el desarrollo personal / Materiales educativos sobre las relaciones de pareja y sexuales, embarazo precoz, maternidad y desarrollo del niño; Instrumentos musicales, juegos, juguetes, artesanías y materiales educativos / Materiales, artículos y suministros didácticos profesionales y para el desarrollo personal / Organismos vivos, especímenes conservados y materiales relacionados; Muebles y mobiliario / Muebles de alojamiento / Accesorios y muebles de bebé y niño; Muebles y mobiliario / Muebles de alojamiento / Muebles para el exterior; Productos de papel / Productos de papel / Papel de imprenta y escritura; Tecnologías de la información, telecomunicaciones y radiodifusión / Equipos informáticos y accesorios / Computadores</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>14111500; 27112000; 30151900; 31211500; 41116200; 42191600; 42301500; 43211500; 44121600; 49121600; 49201600; 50101500; 56101600; 56101800; 60103900; 60105900</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>La Corporación Municipal de Desarrollo Social de Lampa requiere la adquisición de equipos de ejercicio, modelos anatómicos maquetas y maniquíes, incluyendo lactancia, artículos de jardinería y otros artículos, destinados al equipamiento de CECOSF, para apoyar prestaciones de salud, actividades formativas y el mantenimiento de espacios comunitarios.</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>LICITACIONES</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Sargento aldea 898</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>70.954.200-1</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>CRISTIAN MARCELO RIQUELME BECERRA</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Asistente administrativo</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>2026-07-09T20:00:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2026-07-14T15:00:00</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>2026-07-14T15:00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>2026-08-12T20:00:00</t>
-        </is>
-      </c>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Horas</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>NICOLAS GUAJARDO</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Claudia Gonzáles</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>Barras con pesas; Esqueleto, hueso o especímenes de concha; Estacionamientos para bicicletas; Hardware de vías carriles de cortina o biombos o cortinas de cubículo del paciente; Kit de grapadora; Mangas de herramientas; Maniquís humanos anatómicos para formación y estudios de medicina; Materiales educativos de formación sobre cuidado del bebé; Mesas de camping; Monitores o medidores de glucosa; Máquinas de ejercicios múltiples; Notebook, laptop o computador portátil excepto Tablet PC; Papel para impresora del ordenador; Pinturas al esmalte; Toldos; Verduras frescas; mudadores o accesorios</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>852-26-LP26</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>SERVICIO DE MANTENCIÓN DE ÁREAS VERDES MALLECO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Publicada</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Temuco</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>80000000</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-07-14T18:07:12.863</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2026-08-03T16:00:00</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>2026-09-04T18:39:00</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>areas verdes</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>72102900</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>655</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>El objeto de la presente licitación es contratar el “SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES, PROVINCIA DE MALLECO, REGIÓN DE LA ARAUCANÍA AÑO 2026-2028”.</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Junji - IX Región</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VICUÑA MACKENNA 914 </t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>70.072.600-2</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>KARIME HERRERA FIGUEROA</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>PROFESIONAL</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2026-07-21T18:00:00</t>
+          <t>2026-06-30T20:00:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-03T16:10:00</t>
+          <t>2026-07-14T12:01:00</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-08-03T16:10:00</t>
+          <t>2026-07-14T12:01:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>2026-09-04T18:39:00</t>
+          <t>2026-08-31T23:59:00</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr"/>
@@ -3054,7 +3425,7 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -3074,7 +3445,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -3084,23 +3455,23 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>TESORERÍA</t>
+          <t>Carolina Villarroel Cuevas</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>JURÍDICO</t>
+          <t>Carolina Villarroel Cuevas</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>Servicios de paisajismo, arquitectura paisajista</t>
+          <t>Servicios de sembradío o mantenimiento de jardines</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -3110,31 +3481,56 @@
       <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>564953-38-CO26</t>
+          <t>1164956-13-O126</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO DE OBRAS CIVILES JARDIN G. BLANCHE</t>
+          <t xml:space="preserve">Mejoramiento Areas Verdes Plaza Merlot, Comuna de Buin </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>O1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3144,12 +3540,10 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Las Condes</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>24000000</v>
-      </c>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -3157,67 +3551,63 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-29T17:07:50.893</t>
+          <t>2026-06-17T15:16:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-05-14T17:59:00</t>
+          <t>2026-07-15T10:00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-14T15:55:32.273</t>
+          <t>2027-07-15T23:59:00</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+          <t>Consultoria / Consultoria / Planificación y Factibilidad</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>80111600</t>
+          <t>104000000</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Contratar los Servicios de obras para el mejoramiento de obras civiles en camino acceso de Jardín Infantil General Blanche.</t>
+          <t>El objeto de la contratación es la ejecución de obras cuya finalidad es la construcción de áreas verdes.</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Corporación de Educación y Salud de Las Condes</t>
+          <t>Obra Publica</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>RIO LOA 8350 (360 RAM)</t>
+          <t>Serrano #45</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>61.812.000-7</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paola Romero </t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Adquisiciones</t>
-        </is>
-      </c>
+          <t>Karin Kaempfe Vasquez</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
           <t>0</t>
@@ -3227,40 +3617,36 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2026-05-12T18:00:00</t>
+          <t>2026-07-03T13:05:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-15T09:00:00</t>
+          <t>2026-07-15T10:00:00</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-05-18T09:00:00</t>
+          <t>2026-07-15T10:00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>2026-05-29T18:00:00</t>
+          <t>2027-07-15T23:59:00</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
+      <c r="AF14" t="n">
+        <v>0</v>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Horas</t>
-        </is>
+      <c r="AH14" t="n">
+        <v>0</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
@@ -3274,7 +3660,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -3282,17 +3668,9 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Francisco Díaz</t>
-        </is>
-      </c>
+      <c r="AM14" t="inlineStr"/>
       <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Francisco Perez</t>
-        </is>
-      </c>
+      <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr"/>
       <c r="AR14" t="n">
@@ -3300,57 +3678,76 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>Servicios temporales de construcción</t>
+          <t>Licitación Pública de Obra MINVU</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AU14" t="inlineStr"/>
       <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=2GycfPKiV9b5GyZ0QeMzyfCaIb34YH7bccN+uHYh1lA=</t>
-        </is>
-      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1164956-13-O126</t>
+          <t>1469-97-L126</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mejoramiento Areas Verdes Plaza Merlot, Comuna de Buin </t>
+          <t>“ADQUISICIÓN DE ALIMENTOS PARA ANIMALES Y AVES DEL JARDÍN BOTÁNICO Y ARBORETUM, TAL2495, UNIVERSIDAD DE TALCA”</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cerrada</t>
+          <t>Adjudicada</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>O1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION AREA METROPOLITANA</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -3361,63 +3758,69 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-06-17T15:16:00</t>
+          <t>2026-06-19T09:25:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-15T10:00:00</t>
+          <t>2026-06-30T15:00:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2027-07-15T23:59:00</t>
+          <t>2026-07-15T12:12:47.727</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>areas verdes</t>
+          <t>jardin</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Consultoria / Consultoria / Planificación y Factibilidad</t>
+          <t>Artículos para plantas y animales / Alimento para animales / Alimento para aves de corral</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>104000000</t>
+          <t>10121600</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>51</v>
+        <v>206</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>El objeto de la contratación es la ejecución de obras cuya finalidad es la construcción de áreas verdes.</t>
+          <t>La Universidad de Talca requiere la provisión de alimentos para animales y aves
+(silvestres, exóticos y domésticos), aproximadamente 50 especies de la Unidad
+Jardín Botánico y Arboretum.</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Obra Publica</t>
+          <t>Universidad de Talca</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Serrano #45</t>
+          <t>Laboratorio Computacional, Facultad de Psicología, Universidad de Talca, Av. Lircay s/n</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>61.812.000-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Karin Kaempfe Vasquez</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr"/>
+          <t>Yoselin Patricia Pezoa Gonzalez</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ejecutiva de Compras</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>0</t>
@@ -3427,23 +3830,23 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2026-07-03T13:05:00</t>
+          <t>2026-06-25T18:00:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-15T10:00:00</t>
+          <t>2026-06-30T15:01:00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-07-15T10:00:00</t>
+          <t>2026-06-30T15:01:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>2027-07-15T23:59:00</t>
+          <t>2026-07-14T18:00:00</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr"/>
@@ -3484,30 +3887,77 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr"/>
       <c r="AR15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>Licitación Pública de Obra MINVU</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
+          <t>Alimento para aves</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>Autorizacion</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>20-41780</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>2026-07-15T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=mA7sTlI+VVHWPPzHtujxMx36KoDy9SGTBeVJNGdc8NM=</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>PRISCILA DEL ROSARIO ALIAGA NÚÑEZ</t>
+        </is>
+      </c>
       <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1469-97-L126</t>
+          <t>2176-26-LE26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>“ADQUISICIÓN DE ALIMENTOS PARA ANIMALES Y AVES DEL JARDÍN BOTÁNICO Y ARBORETUM, TAL2495, UNIVERSIDAD DE TALCA”</t>
+          <t>Mantención de áreas verdes Juzgado Isla de Pascua</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3517,22 +3967,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -3543,67 +3993,65 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-06-19T09:25:00</t>
+          <t>2026-05-20T20:42:01.457</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-06-30T15:00:00</t>
+          <t>2026-06-01T16:01:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-15T12:12:47.727</t>
+          <t>2026-07-15T15:25:49.42</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Artículos para plantas y animales / Alimento para animales / Alimento para aves de corral</t>
+          <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10121600</t>
+          <t>70111700</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>206</v>
+        <v>275</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>La Universidad de Talca requiere la provisión de alimentos para animales y aves
-(silvestres, exóticos y domésticos), aproximadamente 50 especies de la Unidad
-Jardín Botánico y Arboretum.</t>
+          <t>Servicio de mantenimiento de jardines y espacios verdes</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Universidad de Talca</t>
+          <t>Corp. Adm. del Poder Judicial -  Valparaiso</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Laboratorio Computacional, Facultad de Psicología, Universidad de Talca, Av. Lircay s/n</t>
+          <t>Prat 779, piso 9</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Yoselin Patricia Pezoa Gonzalez</t>
+          <t>ALEJANDRO MUÑOZ</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Ejecutiva de Compras</t>
+          <t>Administrativo de Mantenimiento</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -3615,36 +4063,40 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2026-06-25T18:00:00</t>
+          <t>2026-05-28T15:26:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-30T15:01:00</t>
+          <t>2026-06-01T16:02:00</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-06-30T15:01:00</t>
+          <t>2026-06-01T16:02:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>2026-07-14T18:00:00</t>
+          <t>2026-07-30T10:02:00</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="n">
-        <v>0</v>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Meses</t>
+        </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -3663,61 +4115,94 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr"/>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Victor Villaroel Corrales</t>
+        </is>
+      </c>
       <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Victor Villarroel Corrales</t>
+        </is>
+      </c>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr"/>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>Alimento para aves</t>
+          <t>Servicios de sembradío o mantenimiento de jardines</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>Autorizacion</t>
+          <t>Resolucion</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>20-41780</t>
+          <t>26azvalp N106</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>2026-07-15T00:00:00</t>
+          <t>2026-07-14T00:00:00</t>
         </is>
       </c>
       <c r="AW16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=mA7sTlI+VVHWPPzHtujxMx36KoDy9SGTBeVJNGdc8NM=</t>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=jJu9LyXh6+9s8/BwQv1qmTJxxdIGC6F/G+TBu54mFxk=</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>PRISCILA DEL ROSARIO ALIAGA NÚÑEZ</t>
+          <t>VÍCTOR ANDRÉS VAI MIRI RAGI HAOA HAOA</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2176-26-LE26</t>
+          <t>2585-56-LE26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mantención de áreas verdes Juzgado Isla de Pascua</t>
+          <t>“ADQ. REPUESTOS MAQUINAS PODADORAS ORD.  N°5242026 AREAS VERDES DIMAO IMA”</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3732,17 +4217,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Región de Arica y Parinacota</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Arica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -3753,17 +4238,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-05-20T20:42:01.457</t>
+          <t>2026-06-02T11:55:58.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-06-01T16:01:00</t>
+          <t>2026-06-15T15:01:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2026-07-15T15:25:49.42</t>
+          <t>2026-07-15T10:42:41.77</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -3773,45 +4258,45 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
+          <t>Artículos de fabricación y producción / Cuerdas, cadenas, cables, alambres y correas / Cadenas; Combustibles, lubricantes y anticorrosivos / Lubricantes y anticorrosivos / Lubricantes; Herramientas y maquinaria en general / Herramientas manuales / Herramientas de desbaste y acabado; Resinas, cauchos, espumas y elastómeros / Caucho y elastómeros / Plásticos termoplásticos</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>70111700</t>
+          <t>13102000; 15121500; 27111900; 31151600</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>275</v>
+        <v>2694</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>Servicio de mantenimiento de jardines y espacios verdes</t>
+          <t>La Ilustre Municipalidad de Arica - en adelante "La Municipalidad" - convoca a la licitación denominada “ADQ. REPUESTOS MAQUINAS PODADORAS, ORD.  N°524/2026, AREAS VERDES, DIMAO, IMA, NNR1”, dado la necesidad de la municipalidad de contar con los materiales de construcción y herramientas para el correcto funcionamiento de la oficina de logística, conforme a las especificaciones administrativas, técnicas y económicas establecidas en las presentes bases administrativas y técnicas, anexos y/o formularios</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>Corp. Adm. del Poder Judicial -  Valparaiso</t>
+          <t>FINANZAS IMA</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Prat 779, piso 9</t>
+          <t>AV. RENATO ROCCA 1585</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>ALEJANDRO MUÑOZ</t>
+          <t>Nelson Nuñez Retamal</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Administrativo de Mantenimiento</t>
+          <t>Administrativo</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -3823,23 +4308,23 @@
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2026-05-28T15:26:00</t>
+          <t>2026-06-10T17:30:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-01T16:02:00</t>
+          <t>2026-06-15T15:02:00</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-06-01T16:02:00</t>
+          <t>2026-06-15T15:02:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>2026-07-30T10:02:00</t>
+          <t>2026-09-30T17:30:00</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr"/>
@@ -3850,7 +4335,7 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -3875,94 +4360,119 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Victor Villaroel Corrales</t>
+          <t>MAURICIO ALBANES GOMEZ</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Victor Villarroel Corrales</t>
+          <t>MAURICIO ALBANES GOMEZ</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>Servicios de sembradío o mantenimiento de jardines</t>
+          <t>Aceite de engranajes; Cadenas corrientes; Limas; Nylon - Poliamida (PA)</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>Resolucion</t>
+          <t>Decreto</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>26azvalp N106</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>2026-07-14T00:00:00</t>
+          <t>2026-07-09T00:00:00</t>
         </is>
       </c>
       <c r="AW17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=jJu9LyXh6+9s8/BwQv1qmTJxxdIGC6F/G+TBu54mFxk=</t>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=s7riJfp0D7wlQl+Chjc3TZzhkYAfvRPvhT/Li0w76+g=</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>VÍCTOR ANDRÉS VAI MIRI RAGI HAOA HAOA</t>
+          <t>FERRETERIA AGRICOLA AQUALINE LIMITADA</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2585-56-LE26</t>
+          <t>852-15-LP26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>“ADQ. REPUESTOS MAQUINAS PODADORAS ORD.  N°5242026 AREAS VERDES DIMAO IMA”</t>
+          <t>SERVICIO DE MANTENCIÓN DE ÁREAS VERDES CAUTÍN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Adjudicada</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Arica</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -3973,17 +4483,17 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-06-02T11:55:58.05</t>
+          <t>2026-06-25T12:26:44.457</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-06-15T15:01:00</t>
+          <t>2026-07-15T16:00:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2026-07-15T10:42:41.77</t>
+          <t>2026-07-31T18:00:00</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -3993,45 +4503,46 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Artículos de fabricación y producción / Cuerdas, cadenas, cables, alambres y correas / Cadenas; Combustibles, lubricantes y anticorrosivos / Lubricantes y anticorrosivos / Lubricantes; Herramientas y maquinaria en general / Herramientas manuales / Herramientas de desbaste y acabado; Resinas, cauchos, espumas y elastómeros / Caucho y elastómeros / Plásticos termoplásticos</t>
+          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>13102000; 15121500; 27111900; 31151600</t>
+          <t>72102900</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2694</v>
+        <v>655</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>La Ilustre Municipalidad de Arica - en adelante "La Municipalidad" - convoca a la licitación denominada “ADQ. REPUESTOS MAQUINAS PODADORAS, ORD.  N°524/2026, AREAS VERDES, DIMAO, IMA, NNR1”, dado la necesidad de la municipalidad de contar con los materiales de construcción y herramientas para el correcto funcionamiento de la oficina de logística, conforme a las especificaciones administrativas, técnicas y económicas establecidas en las presentes bases administrativas y técnicas, anexos y/o formularios</t>
+          <t>El objeto de la presente licitación es contratar el “SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES CLÁSICOS, PROVINCIA DE CAUTÍN, REGIÓN DE LA ARAUCANÍA AÑOS 2026-2028”. 
+La contratación del SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES CLÁSICOS, PROVINCIA DE CAUTÍN, REGIÓN DE LA ARAUCANÍA AÑOS 2026-2028” es bajo el sistema de precios unitarios descrito en las bases técnicas de la presente licitación.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>FINANZAS IMA</t>
+          <t>Junji - IX Región</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>AV. RENATO ROCCA 1585</t>
+          <t xml:space="preserve">VICUÑA MACKENNA 914 </t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Nelson Nuñez Retamal</t>
+          <t>KARIME HERRERA FIGUEROA</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Administrativo</t>
+          <t>PROFESIONAL</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -4043,23 +4554,23 @@
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2026-06-10T17:30:00</t>
+          <t>2026-07-02T18:00:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-15T15:02:00</t>
+          <t>2026-07-15T16:01:00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-06-15T15:02:00</t>
+          <t>2026-07-15T16:01:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>2026-09-30T17:30:00</t>
+          <t>2026-07-31T18:00:00</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr"/>
@@ -4070,7 +4581,7 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -4100,92 +4611,97 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>MAURICIO ALBANES GOMEZ</t>
+          <t>TESORERÍA</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>MAURICIO ALBANES GOMEZ</t>
+          <t>JURÍDICO</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr"/>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>Aceite de engranajes; Cadenas corrientes; Limas; Nylon - Poliamida (PA)</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>Decreto</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>8007</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>2026-07-09T00:00:00</t>
-        </is>
-      </c>
-      <c r="AW18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=s7riJfp0D7wlQl+Chjc3TZzhkYAfvRPvhT/Li0w76+g=</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>FERRETERIA AGRICOLA AQUALINE LIMITADA</t>
-        </is>
-      </c>
+          <t>Servicios de paisajismo, arquitectura paisajista</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>852-15-LP26</t>
+          <t>3253-47-LR26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCIÓN DE ÁREAS VERDES CAUTÍN</t>
+          <t>SERVICIO DE MANTENCION AREAS VERDES COMUNA PELLUHUE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cerrada</t>
+          <t>Adjudicada</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Temuco</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>2135000000</v>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -4193,17 +4709,17 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-06-25T12:26:44.457</t>
+          <t>2026-04-30T15:52:56.8</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-15T16:00:00</t>
+          <t>2026-06-01T15:00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-07-31T18:00:00</t>
+          <t>2026-07-15T10:53:57.703</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -4213,46 +4729,45 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
+          <t>Servicios de limpieza industrial / Eliminación y tratamiento de desechos / Recolección y eliminación de desechos</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>72102900</t>
+          <t>76121500</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>655</v>
+        <v>98</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>El objeto de la presente licitación es contratar el “SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES CLÁSICOS, PROVINCIA DE CAUTÍN, REGIÓN DE LA ARAUCANÍA AÑOS 2026-2028”. 
-La contratación del SERVICIO DE MANTENCIÓN DE ÁREAS VERDES EN JARDINES INFANTILES CLÁSICOS, PROVINCIA DE CAUTÍN, REGIÓN DE LA ARAUCANÍA AÑOS 2026-2028” es bajo el sistema de precios unitarios descrito en las bases técnicas de la presente licitación.</t>
+          <t>SE REQUIERE LA CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES, SERVICIO DE RECOLECCION DE RESIDUOS SOLIDOS DOMICILIARIOS, Y SERVICIOS DE ASEO, COMUNA DE PELLUHUE 2026, 2027 Y2028, SEGUN BASES TECNICAS Y ADMINISTRATIVAS</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Junji - IX Región</t>
+          <t>Secretaría de  Planificación</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t xml:space="preserve">VICUÑA MACKENNA 914 </t>
+          <t>Avenida Padre Samuel Jofré 415 Curanipe</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>KARIME HERRERA FIGUEROA</t>
+          <t>JOHANNA ESTUARDO YAÑEZ</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>PROFESIONAL</t>
+          <t>PROFESIONAL EJECUTIVA DE COMPRAS</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -4264,23 +4779,23 @@
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2026-07-02T18:00:00</t>
+          <t>2026-05-18T17:00:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-15T16:01:00</t>
+          <t>2026-06-01T17:01:00</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-07-15T16:01:00</t>
+          <t>2026-06-01T17:01:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>2026-07-31T18:00:00</t>
+          <t>2026-06-29T17:36:00</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr"/>
@@ -4291,7 +4806,7 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -4311,23 +4826,23 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>TESORERÍA</t>
+          <t>MARGARITA VILLASEÑOR JARA</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>JURÍDICO</t>
+          <t>MARIA LUZ REYES ORELLANA</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr"/>
@@ -4337,31 +4852,78 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>Servicios de paisajismo, arquitectura paisajista</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
+          <t>Servicios de limpieza de calles</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>Decreto</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>4960</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>2026-06-17T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=RDr61j8tTf7ceNubu4WgOOc7QobLxxoP/O3g6H8rhMM=</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>INDUSTRIAL SERVICES SPA</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4412-16-LP26</t>
+          <t>3880-46-LP26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEJORAMIENTO AREAS VERDES Y SENDA PEATONAL QUILPUÉ</t>
+          <t>CONSTRUCCIÓN ÁREA VERDE EL MIRADOR III COMUNA DE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Publicada</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4371,20 +4933,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>193990000</v>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -4392,103 +4956,98 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-07-15T13:57:58.64</t>
+          <t>2026-06-25T10:43:34.68</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-14T15:30:00</t>
+          <t>2026-07-15T15:00:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-09-28T15:30:00</t>
+          <t>2026-08-17T10:05:00</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>areas verdes</t>
+          <t>area verde</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>72131700</t>
+          <t>80111600</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>59</v>
+        <v>357</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>El objetivo es la ejecución de los siguientes proyectos:
--Proyecto N°1, que contempla las obras de mejoramiento del área verde ubicada en Avenida Industrial con calle José Uribe, en el sector de Belloto Norte.
--Proyecto N°2, que contempla las obras de mejoramiento del área verde ubicada en calle Cora Wargny, en el sector de El Sol.
--Proyecto N°3, que contempla las obras de mejoramiento de una senda peatonal en sector La Paloma, entre las calles Recoleta y La Paloma.</t>
+          <t>CONSTRUCCIÓN ÁREA VERDE EL MIRADOR III, COMUNA DE MAULE, SECPLAN SEGUN BASES Y ARCHIVOS ADJUNTOS.</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Secretaria Comunal de Planificación</t>
+          <t>Municipalidad de Maule</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>General Velasquez 560</t>
+          <t>Balmaceda 350</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>69.061.300-K</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>SERGIO FRANCISCO ARTEAGA LAZCANO</t>
+          <t>Jaime Meza Valenzuela</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>PROFESIONAL</t>
+          <t>ASISTENTE COORDINACION COMPRAS MUNICIPAL</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2026-08-03T18:30:00</t>
+          <t>2026-07-09T16:00:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-21T15:31:00</t>
+          <t>2026-07-15T15:00:00</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-08-21T15:31:00</t>
+          <t>2026-07-15T15:00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>2026-09-28T15:30:00</t>
+          <t>2026-08-17T10:05:00</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
+      <c r="AF20" t="n">
+        <v>12</v>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
@@ -4512,23 +5071,23 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>ARACELLI ALVAREZ VERGARA</t>
+          <t>Departamento de Finanzas</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>XIMENA OLIVARES CERPA</t>
+          <t>Secretario Comunal de Planificación</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr"/>
@@ -4538,7 +5097,7 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>Construcción de obras civiles</t>
+          <t>Servicios temporales de construcción</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -4548,45 +5107,70 @@
       <c r="AX20" t="inlineStr"/>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="n">
+        <v>64.66333333333333</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3253-47-LR26</t>
+          <t>2289-33-LP26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SERVICIO DE MANTENCION AREAS VERDES COMUNA PELLUHUE</t>
+          <t>CONSTRUCCION MULTICANCHA Y MEJORAMIENTO AREA VERDE VILLAS UNIDAS FRUTILLAR</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Adjudicada</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t xml:space="preserve">Región de los Lagos </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelluhue</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2135000000</v>
+        <v>164509829</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -4595,65 +5179,65 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-04-30T15:52:56.8</t>
+          <t>2026-06-17T08:34:52</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-06-01T15:00:00</t>
+          <t>2026-07-17T15:05:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-07-15T10:53:57.703</t>
+          <t>2026-08-03T13:00:00</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>areas verdes</t>
+          <t>area verde</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Servicios de limpieza industrial / Eliminación y tratamiento de desechos / Recolección y eliminación de desechos</t>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>76121500</t>
+          <t>72131700</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>98</v>
+        <v>324</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>SE REQUIERE LA CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES, SERVICIO DE RECOLECCION DE RESIDUOS SOLIDOS DOMICILIARIOS, Y SERVICIOS DE ASEO, COMUNA DE PELLUHUE 2026, 2027 Y2028, SEGUN BASES TECNICAS Y ADMINISTRATIVAS</t>
+          <t>La presente licitación tiene por objeto la contratación de la ejecución de la obra "CONSTRUCCION MULTICANCHA RECREATIVA Y MEJORAMIENTO AREA VERDE, VILLAS UNIDAS, COMUNA DE FRUTILLAR"</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Secretaría de  Planificación</t>
+          <t>MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Avenida Padre Samuel Jofré 415 Curanipe</t>
+          <t>AVDA. ALESSANDRI S/N FRENTE A PLAZA FRUTILLAR ALTO</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>JOHANNA ESTUARDO YAÑEZ</t>
+          <t xml:space="preserve">Victor Hugo Mayorga Alvarado  </t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>PROFESIONAL EJECUTIVA DE COMPRAS</t>
+          <t>Adm. secplac</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -4665,23 +5249,23 @@
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2026-05-18T17:00:00</t>
+          <t>2026-07-07T18:00:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-01T17:01:00</t>
+          <t>2026-07-20T09:00:00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-06-01T17:01:00</t>
+          <t>2026-07-20T09:00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>2026-06-29T17:36:00</t>
+          <t>2026-08-03T13:00:00</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr"/>
@@ -4692,12 +5276,12 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Meses</t>
+          <t>Horas</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
@@ -4722,13 +5306,13 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>MARGARITA VILLASEÑOR JARA</t>
+          <t>GILDA ALVARADO</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>MARIA LUZ REYES ORELLANA</t>
+          <t>CRISTABEL GALLEGOS</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr"/>
@@ -4738,77 +5322,80 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>Servicios de limpieza de calles</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>Decreto</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>4960</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>2026-06-17T00:00:00</t>
-        </is>
-      </c>
-      <c r="AW21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=RDr61j8tTf7ceNubu4WgOOc7QobLxxoP/O3g6H8rhMM=</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>INDUSTRIAL SERVICES SPA</t>
-        </is>
-      </c>
+          <t>Construcción de obras civiles</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="n">
+        <v>54.83660966666667</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>88</v>
+      </c>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2859-31-LP26</t>
+          <t>3775-22-LR26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SERVICIO DE ASEO JARDINERIA Y GASFITERÍA</t>
+          <t>Mantención Áreas Verdes y Emergencias en Hijuelas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Publicada</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Hijuelas</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>300000000</v>
+        <v>480000000</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -4817,93 +5404,93 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-07-15T13:32:59.52</t>
+          <t>2026-06-16T17:05:23.057</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-04T18:00:00</t>
+          <t>2026-07-17T15:01:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-08-14T19:00:00</t>
+          <t>2026-08-31T18:00:00</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Servicios de limpieza industrial / Servicios de limpieza / Servicios de limpieza de edificios y oficinas en general</t>
+          <t>Servicios de limpieza industrial / Eliminación y tratamiento de desechos / Recolección y eliminación de desechos</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>76111500</t>
+          <t>76121500</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>373</v>
+        <v>120</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>SERVICIO DE ASEO, JARDINERIA Y GASFITERÍA PARA LA FACULTAD DE CIENCIAS DE LA SALUD CAMPUS CORDILLERA Y  CASA MALDINI” DE LA UNIVERSIDAD DE ATACAMA.</t>
+          <t>“SERVICIO DE MANTENCIÓN, MEJORAMIENTO DE ÁREAS VERDES Y SERVICIO DE EMERGENCIAS PARA LABORES PREVENTIVAS, OPERATIVAS Y DE OBRAS MENORES EN COMUNA DE HIJUELAS”</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>SECCIÓN ABASTECIMIENTO</t>
+          <t>Secretaria Comunal De Planificacion</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>COPAYAPU Nº 485 COPIAPÓ</t>
+          <t>MANUEL RODRIGUEZ #1665, HIJUELAS</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Natalia Acuña Delgado</t>
+          <t>Cristian Briones Arraño</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>Asistente Administrativa</t>
+          <t>Profesional Secplan</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>2026-07-24T18:00:00</t>
+          <t>2026-06-26T18:00:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-04T18:01:00</t>
+          <t>2026-07-17T15:02:00</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-08-04T18:01:00</t>
+          <t>2026-07-17T15:02:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>2026-08-14T19:00:00</t>
+          <t>2026-08-31T18:00:00</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr"/>
@@ -4944,13 +5531,13 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>DANIEL HERNANDEZ MANCILLA</t>
+          <t>Claudio Jamet Amaro</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>WILSON JOPIA CARMONA</t>
+          <t>Felipe Durán Rojas</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr"/>
@@ -4960,7 +5547,7 @@
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>Servicios de limpieza de edificios</t>
+          <t>Servicios de limpieza de calles</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -4970,31 +5557,56 @@
       <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="n">
+        <v>100</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>100</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5300-51-LP26</t>
+          <t>3882-58-LE26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSTRUCCION CANCHA DE PASTO SINTETICO Y AREA VERDE HUMBERTO MOATH </t>
+          <t>MEJORAMIENTO BODEGA MUNICIPAL AREAS VERDES COMUNA DE LLAY LLAY</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Publicada</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5004,7 +5616,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Casablanca</t>
+          <t>Llay-Llay</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -5015,22 +5627,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-07-15T15:42:48.71</t>
+          <t>2026-07-01T15:38:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-10T15:00:00</t>
+          <t>2026-07-17T15:10:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-08-24T18:00:00</t>
+          <t>2026-07-31T17:00:00</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>area verde</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -5044,71 +5656,64 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>222</v>
+        <v>70</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>La necesidad de intervenir y consolidar un espacio recreativo integral en la
-Villa Humberto Moath, mediante la transformación de la actual cancha de
-tierra en un complejo deportivo de pasto sintético dotado de sistemas de
-drenaje y canalización de aguas lluvias. Esta obra busca revertir el avanzado
-deterioro del sector y sus problemas de anegamiento invernal,
-promoviendo el desarrollo sustentable y la revitalización del entorno
-urbano de Casablanca para fortalecer el sentido de comunidad en sus
-habitantes.</t>
+          <t>Se requiere contratar empresa idonea para ejecutar las obras correspondientes a  el mejoramiento del comedor, cocina, baños, camarines, pavimento patio exterior, sistema alcantarillado y agua potable, de recinto municipal siguiendo como referencia las especificaciones tecnicas.</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>DIPLAD</t>
+          <t>Ilustre Municipalidad de Llay Llay</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>CONSTITUCION 111</t>
+          <t>Avda. Balmaceda 174</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>FELIPE EDUARDO NUÑEZ CHEUQUE</t>
+          <t>Cesar Ignacio Lobos Espinoza</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>ARQUITECTO</t>
+          <t>Profesional SECPLAC</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>2026-07-29T18:00:00</t>
+          <t>2026-07-10T13:00:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-10T15:05:00</t>
+          <t>2026-07-17T15:10:00</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-08-10T15:05:00</t>
+          <t>2026-07-17T15:30:00</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>2026-08-24T18:00:00</t>
+          <t>2026-07-31T17:00:00</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr"/>
@@ -5119,7 +5724,7 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -5149,13 +5754,13 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>VICTOR QUINTEROS</t>
+          <t xml:space="preserve">I Municipalidad de Llay Llay </t>
         </is>
       </c>
       <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>YURI RODRIGUEZ REYES</t>
+          <t xml:space="preserve">I Municipalidad de Llay Llay </t>
         </is>
       </c>
       <c r="AP23" t="inlineStr"/>
@@ -5175,16 +5780,41 @@
       <c r="AX23" t="inlineStr"/>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3880-46-LP26</t>
+          <t>707423-49-LE26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN ÁREA VERDE EL MIRADOR III COMUNA DE</t>
+          <t>ROPA DE CAMA PARA JARDINES Y SALAS CUNA ARAUCANIA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5194,26 +5824,26 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t xml:space="preserve">Región de la Araucanía </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Temuco</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>193990000</v>
+        <v>46300000</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -5222,65 +5852,65 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-06-25T10:43:34.68</t>
+          <t>2026-06-18T09:49:03.22</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-15T15:00:00</t>
+          <t>2026-07-17T15:01:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-08-17T10:05:00</t>
+          <t>2026-08-11T16:30:00</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>area verde</t>
+          <t>jardin; jardines</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
+          <t>Muebles, accesorios, electrodomésticos y productos electrónicos / Ropa de cama, mantelerías, paños de cocina y toallas / Ropa de cama</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>80111600</t>
+          <t>52121500</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>357</v>
+        <v>31</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>CONSTRUCCIÓN ÁREA VERDE EL MIRADOR III, COMUNA DE MAULE, SECPLAN SEGUN BASES Y ARCHIVOS ADJUNTOS.</t>
+          <t>Fundación Integra, requiere de la adquisición de textiles, ropa de cama para jardines infantiles, salas cuna y oficina regional de fundación integra, Araucanía de conformidad a lo señalado en las presentes Bases Administrativas Especiales, Bases Administrativas Generales, Bases Técnicas, y Anexos.</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Municipalidad de Maule</t>
+          <t>Regional Araucania</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Balmaceda 350</t>
+          <t>Claro Solar Nº 1148</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Jaime Meza Valenzuela</t>
+          <t>Paola Macarena San Martín</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>ASISTENTE COORDINACION COMPRAS MUNICIPAL</t>
+          <t>Analista</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -5292,28 +5922,30 @@
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2026-07-09T16:00:00</t>
+          <t>2026-07-02T18:00:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-07-15T15:00:00</t>
+          <t>2026-07-17T15:05:00</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-07-15T15:00:00</t>
+          <t>2026-07-17T15:05:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>2026-08-17T10:05:00</t>
+          <t>2026-08-11T16:30:00</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="n">
-        <v>12</v>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Pago a 30 dias</t>
+        </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
@@ -5347,23 +5979,23 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Departamento de Finanzas</t>
+          <t>MARIELA GARRIDO</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Secretario Comunal de Planificación</t>
+          <t>Patricio Hernandez Rojas</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>Servicios temporales de construcción</t>
+          <t>Almohadas; Cobertor acolchado o plumón; Mantas o frazadas; Sábanas</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -5373,46 +6005,69 @@
       <c r="AX24" t="inlineStr"/>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="n">
+        <v>15.43333333333333</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH24" t="inlineStr"/>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057500-57-LP26</t>
+          <t>4168-68-LE26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SERVICIOS MANTENCION JARDINES Y AREAS VERDES</t>
+          <t>CONCESIÓN MANTENCIÓN ÁREAS VERDES VILLA NUEVA PANIMÁVIDA Y RARIMÁVIDA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Publicada</t>
+          <t>Adjudicada</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR ORIENTE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región del Maule </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>270000000</v>
-      </c>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -5420,101 +6075,96 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-07-17T11:14:49.44</t>
+          <t>2026-06-15T17:41:09.183</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-10T15:01:00</t>
+          <t>2026-06-25T11:00:00</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-09-28T19:00:00</t>
+          <t>2026-07-17T12:03:47.713</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>jardin; jardines; areas verdes</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
+          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>70111700</t>
+          <t>72102900</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>386</v>
+        <v>485</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE REQUIERE LA CONTRATACIÓN DEL SERVICIO DE MANTENIMIENTO DE JARDÍNES Y ÁREAS VERDES PARA DEPENDENCIAS DE LA DIRECCIÓN DEL SERVICIO DE SALUD METROPOLITANO SUR ORIENTE, SEGÚN BASES APROBADAS POR RES. EXENTA N°1707/2026. 
-</t>
+          <t>La Ilustre Municipalidad de Colbún, en adelante la “Municipalidad”, como Mandante y Unidad Técnica, llama a propuesta pública para contratar la concesión para mantención de las áreas verdes de las Villas Nueva Panimávida y Rarimávida de acuerdo a las Bases Administrativas y otros antecedentes de licitación.</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Municipalidad</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Av. Concha y Toro Nº 3459</t>
+          <t>Adolfo Novoa 419</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>61.608.500-K</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Mauricio Claudio Muñoz Garcia</t>
+          <t>Camilo Ignacio Sepulveda Tobar</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>Profesional Compras</t>
+          <t>ASISTENTE DE SEPCLA</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>2026-07-30T18:00:00</t>
+          <t>2026-06-22T21:24:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-08-10T15:02:00</t>
+          <t>2026-06-25T13:00:00</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-08-10T15:02:00</t>
+          <t>2026-06-25T13:00:00</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>2026-09-28T19:00:00</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>2026-10-16T00:00:00</t>
-        </is>
-      </c>
+          <t>2026-07-30T16:36:00</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr">
         <is>
           <t>Pago a 30 dias</t>
@@ -5522,7 +6172,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -5542,7 +6192,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -5552,13 +6202,13 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Jonathan Levican Reyes</t>
+          <t>Luis Muñoz Torres</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Víctor Araya Retamal</t>
+          <t>Yesica Gonzáles Parra</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr"/>
@@ -5568,51 +6218,98 @@
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>Servicios de sembradío o mantenimiento de jardines</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
+          <t>Servicios de barrido de carreteras o aparcamientos (estacionamientos)</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>Decreto</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>2026-07-13T00:00:00</t>
+        </is>
+      </c>
+      <c r="AW25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=6Jmg7by7tUE+1k0PNqjfP1V4ZIDzKLz1x2dYp6b9PJs=</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>DOMINGO ANTONIO ALFARO VASQUEZ</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>35</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>82</v>
+      </c>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH25" t="inlineStr"/>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1219241-5-LE26</t>
+          <t>4412-13-LP26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Adquisición de 2 Chipeadoras para áreas verdes.</t>
+          <t>MEJORAMIENTOS PLAZOLETAS Y ÁREA VERDE QUILPUÉ 1.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Publicada</t>
+          <t>Cerrada</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LE</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL PUEBLITO DE LAS VIZCACHAS</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Puente Alto</t>
+          <t>Quilpué</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -5623,100 +6320,98 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-07-17T18:07:50.497</t>
+          <t>2026-06-16T16:43:35.693</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-23T16:20:00</t>
+          <t>2026-07-17T15:30:00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-25T17:00:00</t>
+          <t>2026-08-31T15:30:00</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>areas verdes</t>
+          <t>area verde</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Servicios de producción y fabricación industrial / Fabricación de maquinarias y equipos de transporte / Fabricación de maquinarias</t>
+          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>73161500</t>
+          <t>72131700</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Adquisición de dos 2 chipeadoras nuevas para la ejecución de labores de manejo y reducción de residuos vegetales provenientes de trabajos de poda, mantención de áreas verdes y manejo forestal. Los oferentes deberán presentar una cotización detallada, conforme a las especificaciones técnicas adjuntas, indicando como mínimo la marca, modelo, características técnicas del equipo ofertado, plazo de entrega, garantía y cualquier otro antecedente que permita verificar el cumplimiento íntegro de los requerimientos establecidos. Solo se evaluarán las ofertas que cumplan con las especificaciones técnicas solicitadas.</t>
+          <t>-Proyecto N°1, que contempla las obras de mejoramiento de la plazoleta ubicada en la esquina de calles Buzo Sobenes con Almirante Gerken, en población Teniente Serrano.
+-Proyecto N°2, que contempla las obras de mejoramiento de la plazoleta ubicada en la esquina de calles Lago Lanalhue con Marga Marga, en población Porvenir.
+-Proyecto N°3, que contempla las obras de mejoramiento del área verde ubicado en la esquina de calles Ramón Ángel Jara con Marga Marga, en población Ingeniero Hyatt.</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE ADQUISICIONES</t>
+          <t>Secretaria Comunal de Planificación</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Camino San José de Maipo 05109</t>
+          <t>General Velasquez 560</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>65.108.319-2</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>LARISA LEGUIZAMON</t>
+          <t>SERGIO FRANCISCO ARTEAGA LAZCANO</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>COORDINADORA</t>
+          <t>PROFESIONAL</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>2026-07-20T09:00:00</t>
+          <t>2026-07-03T18:30:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-07-23T21:00:00</t>
+          <t>2026-07-17T15:31:00</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-07-23T21:00:00</t>
+          <t>2026-07-17T15:31:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>2026-07-25T17:00:00</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>2026-07-27T00:00:00</t>
-        </is>
-      </c>
+          <t>2026-08-31T15:30:00</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr">
         <is>
           <t>Pago a 30 dias</t>
@@ -5754,13 +6449,13 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Larissa Leguizamon</t>
+          <t>ARACELLI ALVAREZ VERGARA</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Claudio Aranguiz</t>
+          <t>XIMENA OLIVARES CERPA</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr"/>
@@ -5770,7 +6465,7 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>Servicios de fabricación de maquinaria o equipos agrícolas</t>
+          <t>Construcción de obras civiles</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -5780,16 +6475,41 @@
       <c r="AX26" t="inlineStr"/>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
+      <c r="BA26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>100</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH26" t="inlineStr"/>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2289-33-LP26</t>
+          <t>3656-139-L126</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CONSTRUCCION MULTICANCHA Y MEJORAMIENTO AREA VERDE VILLAS UNIDAS FRUTILLAR</t>
+          <t>CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES Y RIEGO DE BIENES NACIONALES DE USO PUBLICO PARA LA MUNICIPALIDAD DE REQUÍNOA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5799,27 +6519,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE REQUINOA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frutillar</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>164509829</v>
-      </c>
+          <t>Requinoa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -5827,65 +6545,65 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-06-17T08:34:52</t>
+          <t>2026-07-10T13:29:39.443</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-17T15:05:00</t>
+          <t>2026-07-17T15:01:00</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-08-03T13:00:00</t>
+          <t>2026-07-29T18:09:00</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>area verde</t>
+          <t>areas verdes</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
+          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>72131700</t>
+          <t>80111600</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>324</v>
+        <v>171</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>La presente licitación tiene por objeto la contratación de la ejecución de la obra "CONSTRUCCION MULTICANCHA RECREATIVA Y MEJORAMIENTO AREA VERDE, VILLAS UNIDAS, COMUNA DE FRUTILLAR"</t>
+          <t>CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES Y RIEGO DE BIENES NACIONALES DE USO PUBLICO PARA LA MUNICIPALIDAD DE REQUÍNOA</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>Ilustre Municipalidad de Requínoa</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>AVDA. ALESSANDRI S/N FRENTE A PLAZA FRUTILLAR ALTO</t>
+          <t>Comercio 121 Municipalidad de Requínoa</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.081.300-9</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Victor Hugo Mayorga Alvarado  </t>
+          <t>MARIANELA ROJAS</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>Adm. secplac</t>
+          <t>MERCADO PUBLICO</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -5897,23 +6615,23 @@
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>2026-07-07T18:00:00</t>
+          <t>2026-07-15T10:00:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-07-20T09:00:00</t>
+          <t>2026-07-17T15:02:00</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-07-20T09:00:00</t>
+          <t>2026-07-17T15:02:00</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>2026-08-03T13:00:00</t>
+          <t>2026-07-29T18:09:00</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr"/>
@@ -5924,12 +6642,12 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Horas</t>
+          <t>Meses</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
@@ -5944,7 +6662,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -5954,23 +6672,23 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>GILDA ALVARADO</t>
+          <t xml:space="preserve">DIEGO MORALES </t>
         </is>
       </c>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>CRISTABEL GALLEGOS</t>
+          <t xml:space="preserve">DIEGO MORALES </t>
         </is>
       </c>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>Construcción de obras civiles</t>
+          <t>Mano de obra temporal</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -5980,31 +6698,56 @@
       <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>93.7</v>
+      </c>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH27" t="inlineStr"/>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>584264-33-LR26</t>
+          <t>5482-75-LE26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MANT. AREAS VERDES COMUNA INDEPENDENCIA</t>
+          <t>Implementación de áreas verdes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Publicada</t>
+          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LR</t>
+          <t>LE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6014,10 +6757,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Independencia</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Ñuñoa</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>60000000</v>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>CLP</t>
@@ -6025,17 +6770,17 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-07-17T11:09:49.967</t>
+          <t>2026-07-08T08:50:48.033</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-17T15:05:00</t>
+          <t>2026-07-17T15:01:00</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-10-06T17:30:00</t>
+          <t>2026-08-31T17:45:00</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -6045,836 +6790,18 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Horticultura / Parques, jardines y huertos</t>
+          <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Producción, administración y protección de cultivos / Sembradío de plantaciones y cultivos</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>70111700</t>
+          <t>70141800</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1291</v>
+        <v>277</v>
       </c>
       <c r="Q28" t="inlineStr">
-        <is>
-          <t>Asegurar la mantención, mejoramiento, reparación, construcción y desarrollo integral de las áreas verdes de la comuna de Independencia, garantizando la limpieza constante y completa de todos los espacios de plaza dura, caminerías, mobiliario urbano y zonas vegetales. Lo anterior se señala como referencia, el oferente deberá regirse por lo señalado en las Bases Técnicas y anexos.</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>DIRECCION DE SECPLA</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>AVDA. INDEPENDENCIA N° 753, INDEPENDENCIA</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>69.255.500-7</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Katherine Ruiz</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Profesional Licitaciones</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>2026-08-06T18:00:00</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-08-17T15:10:00</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>2026-08-17T15:10:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>2026-10-06T17:30:00</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Meses</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>LUIS MEDEL FLORES</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>MARTA OLGUIN COUSIÑO</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>Servicios de sembradío o mantenimiento de parques</t>
-        </is>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>3656-139-L126</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES Y RIEGO DE BIENES NACIONALES DE USO PUBLICO PARA LA MUNICIPALIDAD DE REQUÍNOA</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE REQUINOA</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Requinoa</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-07-10T13:29:39.443</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:01:00</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>2026-07-29T18:09:00</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>areas verdes</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>Servicios profesionales, administrativos y consultorías de gestión empresarial / Servicios de recursos humanos / Servicios de personal temporal</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>80111600</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>171</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>CONTRATACION DE SERVICIO DE MANTENCION DE AREAS VERDES Y RIEGO DE BIENES NACIONALES DE USO PUBLICO PARA LA MUNICIPALIDAD DE REQUÍNOA</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>Ilustre Municipalidad de Requínoa</t>
-        </is>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>Comercio 121 Municipalidad de Requínoa</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>69.081.300-9</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>MARIANELA ROJAS</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>MERCADO PUBLICO</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>2026-07-15T10:00:00</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:02:00</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:02:00</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>2026-07-29T18:09:00</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Meses</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIEGO MORALES </t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DIEGO MORALES </t>
-        </is>
-      </c>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS29" t="inlineStr">
-        <is>
-          <t>Mano de obra temporal</t>
-        </is>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>4168-68-LE26</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>CONCESIÓN MANTENCIÓN ÁREAS VERDES VILLA NUEVA PANIMÁVIDA Y RARIMÁVIDA</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Adjudicada</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región del Maule </t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Colbún</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-06-15T17:41:09.183</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>2026-06-25T11:00:00</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>2026-07-17T12:03:47.713</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>areas verdes</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>Servicios de construcción y mantenimiento / Servicios de atención, mantenimiento y reparaciones de edificios / Servicios de mantenimiento de terrenos</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>72102900</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>485</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>La Ilustre Municipalidad de Colbún, en adelante la “Municipalidad”, como Mandante y Unidad Técnica, llama a propuesta pública para contratar la concesión para mantención de las áreas verdes de las Villas Nueva Panimávida y Rarimávida de acuerdo a las Bases Administrativas y otros antecedentes de licitación.</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>Municipalidad</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Adolfo Novoa 419</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>69.130.500-7</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Camilo Ignacio Sepulveda Tobar</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>ASISTENTE DE SEPCLA</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>2026-06-22T21:24:00</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-06-25T13:00:00</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>2026-06-25T13:00:00</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>2026-07-30T16:36:00</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Meses</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Luis Muñoz Torres</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Yesica Gonzáles Parra</t>
-        </is>
-      </c>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS30" t="inlineStr">
-        <is>
-          <t>Servicios de barrido de carreteras o aparcamientos (estacionamientos)</t>
-        </is>
-      </c>
-      <c r="AT30" t="inlineStr">
-        <is>
-          <t>Decreto</t>
-        </is>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
-      <c r="AV30" t="inlineStr">
-        <is>
-          <t>2026-07-13T00:00:00</t>
-        </is>
-      </c>
-      <c r="AW30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=6Jmg7by7tUE+1k0PNqjfP1V4ZIDzKLz1x2dYp6b9PJs=</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>DOMINGO ANTONIO ALFARO VASQUEZ</t>
-        </is>
-      </c>
-      <c r="AZ30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>4412-13-LP26</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MEJORAMIENTOS PLAZOLETAS Y ÁREA VERDE QUILPUÉ 1.</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>I. MUNICIPALIDAD DE QUILPUE</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-06-16T16:43:35.693</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:30:00</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>2026-08-31T15:30:00</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>area verde</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>72131700</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>59</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>-Proyecto N°1, que contempla las obras de mejoramiento de la plazoleta ubicada en la esquina de calles Buzo Sobenes con Almirante Gerken, en población Teniente Serrano.
--Proyecto N°2, que contempla las obras de mejoramiento de la plazoleta ubicada en la esquina de calles Lago Lanalhue con Marga Marga, en población Porvenir.
--Proyecto N°3, que contempla las obras de mejoramiento del área verde ubicado en la esquina de calles Ramón Ángel Jara con Marga Marga, en población Ingeniero Hyatt.</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Secretaria Comunal de Planificación</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>General Velasquez 560</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>69.061.300-K</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>SERGIO FRANCISCO ARTEAGA LAZCANO</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>PROFESIONAL</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>2026-07-03T18:30:00</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:31:00</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:31:00</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>2026-08-31T15:30:00</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Horas</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>ARACELLI ALVAREZ VERGARA</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>XIMENA OLIVARES CERPA</t>
-        </is>
-      </c>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>Construcción de obras civiles</t>
-        </is>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>5482-75-LE26</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Implementación de áreas verdes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Ñuñoa</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>60000000</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-07-08T08:50:48.033</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:01:00</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>2026-08-31T17:45:00</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>areas verdes</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>Servicios agrícolas, pesqueros, forestales y relacionados con la fauna / Producción, administración y protección de cultivos / Sembradío de plantaciones y cultivos</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>70141800</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>277</v>
-      </c>
-      <c r="Q32" t="inlineStr">
         <is>
           <t xml:space="preserve">Implementación de una nueva área verde con diversidad de especies nativas, consolidando un Bosque de Bolsillo, en el Parque
 Botánico de la comuna, las cuales tienen como objetivo regenerar suelos degradados de manera rápida y eficiente teniendo una alta
@@ -6884,931 +6811,383 @@
 </t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>SECPLANUNOA</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>AV. IRARRAZAVAL 3550 - PISO 3º. SECPLA</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>69.070.500-1</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>JUAN PABLO JIMENEZ TORRES</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>PROFESIONAL SECPLA</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr">
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>2026-07-14T18:00:00</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>2026-07-17T15:02:00</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>2026-07-17T15:02:00</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr">
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr">
         <is>
           <t>2026-08-31T17:45:00</t>
         </is>
       </c>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr">
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr">
         <is>
           <t>Pago a 30 dias</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH32" t="inlineStr">
+      <c r="AH28" t="inlineStr">
         <is>
           <t>Meses</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AK32" t="inlineStr">
+      <c r="AK28" t="inlineStr">
         <is>
           <t>Si</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AM28" t="inlineStr">
         <is>
           <t>alejandra naranjo</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr">
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr">
         <is>
           <t>nicolas preus</t>
         </is>
       </c>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="n">
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="n">
         <v>1</v>
       </c>
-      <c r="AS32" t="inlineStr">
+      <c r="AS28" t="inlineStr">
         <is>
           <t>Servicios de sembradío de cultivos</t>
         </is>
       </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="n">
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="inlineStr"/>
+      <c r="AV28" t="inlineStr"/>
+      <c r="AW28" t="n">
         <v>0</v>
       </c>
-      <c r="AX32" t="inlineStr">
+      <c r="AX28" t="inlineStr">
         <is>
           <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=1efMHKv/qfhpYYOSbY/IMxp4XHEr9tdfzFxW4Zetmf0=</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr"/>
+      <c r="BA28" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>70</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH28" t="inlineStr"/>
+      <c r="BI28" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>2673-45-LE26</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>ADQUISICION INSUMOS Y ACCESORIOS AREAS VERDES</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Desierta (o art. 3 ó 9 Ley 19.886)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>LE</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>ILUSTRE MUNICIPALIDAD DE MELIPILLA</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Melipilla</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
         <is>
           <t>CLP</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>2026-05-29T15:54:52.15</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>2026-06-19T10:00:00</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>2026-07-17T12:18:44.82</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>areas verdes</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Equipamiento para el acondicionamiento, distribución y filtrado de fluidos / Bombas y compresores industriales / Bombas</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>40151500</t>
         </is>
       </c>
-      <c r="P33" t="n">
+      <c r="P29" t="n">
         <v>392</v>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>“ADQUISICIÓN INSUMOS Y ACCESORIOS PARA DEPARTAMENTO DE AREAS VERDES DGA”</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>SECRETARIA PLANIFICACION</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>SILVA CHAVEZ   480</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>69.072.900-8</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>Francisco José Sandoval Domínguez</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>SUPERVISOR</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr">
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>2026-06-11T16:00:00</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>2026-06-19T10:15:00</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>2026-06-19T10:15:00</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr">
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
         <is>
           <t>2026-08-19T19:56:00</t>
         </is>
       </c>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr">
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
         <is>
           <t>Pago a 30 dias</t>
         </is>
       </c>
-      <c r="AG33" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AH33" t="inlineStr">
+      <c r="AH29" t="inlineStr">
         <is>
           <t>Horas</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
+      <c r="AI29" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AK33" t="inlineStr">
+      <c r="AK29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AL33" t="inlineStr">
+      <c r="AL29" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AM29" t="inlineStr">
         <is>
           <t>MARCIA WERCHEZ SANTIBAÑEZ</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr">
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr">
         <is>
           <t>FLORENCIO VALDOVINOS REYES</t>
         </is>
       </c>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="n">
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="n">
         <v>1</v>
       </c>
-      <c r="AS33" t="inlineStr">
+      <c r="AS29" t="inlineStr">
         <is>
           <t>Bombas de agua</t>
         </is>
       </c>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="n">
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="n">
         <v>2</v>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>http://www.mercadopublico.cl/Procurement/Modules/RFB/StepsProcessAward/PreviewAwardAct.aspx?qs=1mm3A2VlyIWnVXkWujQQGu3PEXnbiLZd7m45lKm3Ns0=</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>3775-22-LR26</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Mantención Áreas Verdes y Emergencias en Hijuelas</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>LR</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Hijuelas</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>480000000</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-06-16T17:05:23.057</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:01:00</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>2026-08-31T18:00:00</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>areas verdes</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Servicios de limpieza industrial / Eliminación y tratamiento de desechos / Recolección y eliminación de desechos</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>76121500</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>120</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>“SERVICIO DE MANTENCIÓN, MEJORAMIENTO DE ÁREAS VERDES Y SERVICIO DE EMERGENCIAS PARA LABORES PREVENTIVAS, OPERATIVAS Y DE OBRAS MENORES EN COMUNA DE HIJUELAS”</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Secretaria Comunal De Planificacion</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>MANUEL RODRIGUEZ #1665, HIJUELAS</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>69.060.500-7</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>Cristian Briones Arraño</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>Profesional Secplan</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>2026-06-26T18:00:00</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:02:00</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:02:00</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>2026-08-31T18:00:00</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Meses</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Claudio Jamet Amaro</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Felipe Durán Rojas</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS34" t="inlineStr">
-        <is>
-          <t>Servicios de limpieza de calles</t>
-        </is>
-      </c>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>3882-58-LE26</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>MEJORAMIENTO BODEGA MUNICIPAL AREAS VERDES COMUNA DE LLAY LLAY</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Llay-Llay</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-07-01T15:38:00</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:10:00</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>2026-07-31T17:00:00</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>areas verdes</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Servicios de construcción y mantenimiento / Construcción de edificios en general / Construcción de obras civiles y infraestructuras</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>72131700</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB29" t="n">
         <v>70</v>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Se requiere contratar empresa idonea para ejecutar las obras correspondientes a  el mejoramiento del comedor, cocina, baños, camarines, pavimento patio exterior, sistema alcantarillado y agua potable, de recinto municipal siguiendo como referencia las especificaciones tecnicas.</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Ilustre Municipalidad de Llay Llay</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>Avda. Balmaceda 174</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>69.060.400-0</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Cesar Ignacio Lobos Espinoza</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Profesional SECPLAC</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>2026-07-10T13:00:00</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:10:00</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:30:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>2026-07-31T17:00:00</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Dias</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I Municipalidad de Llay Llay </t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I Municipalidad de Llay Llay </t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS35" t="inlineStr">
-        <is>
-          <t>Construcción de obras civiles</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr"/>
-      <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>707423-49-LE26</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>ROPA DE CAMA PARA JARDINES Y SALAS CUNA ARAUCANIA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Cerrada</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LE</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Temuco</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>46300000</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-06-18T09:49:03.22</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:01:00</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>2026-08-11T16:30:00</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>jardin; jardines</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Muebles, accesorios, electrodomésticos y productos electrónicos / Ropa de cama, mantelerías, paños de cocina y toallas / Ropa de cama</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>52121500</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>31</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Fundación Integra, requiere de la adquisición de textiles, ropa de cama para jardines infantiles, salas cuna y oficina regional de fundación integra, Araucanía de conformidad a lo señalado en las presentes Bases Administrativas Especiales, Bases Administrativas Generales, Bases Técnicas, y Anexos.</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Regional Araucania</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>Claro Solar Nº 1148</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>70.574.900-0</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Paola Macarena San Martín</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Analista</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>2026-07-02T18:00:00</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:05:00</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>2026-07-17T15:05:00</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>2026-08-11T16:30:00</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>Pago a 30 dias</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Horas</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>MARIELA GARRIDO</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Patricio Hernandez Rojas</t>
-        </is>
-      </c>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS36" t="inlineStr">
-        <is>
-          <t>Almohadas; Cobertor acolchado o plumón; Mantas o frazadas; Sábanas</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
+      <c r="BC29" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="n">
+        <v>50</v>
+      </c>
+      <c r="BH29" t="inlineStr"/>
+      <c r="BI29" t="inlineStr">
+        <is>
+          <t>No (historial)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
